--- a/output/yearly_surface_area_iteration_38_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_38_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497624314617</v>
+        <v>10.84497635273064</v>
       </c>
       <c r="C21" t="n">
-        <v>37.789071631551</v>
+        <v>37.78907201339558</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.755405952922303</v>
+        <v>5.584180941755857</v>
       </c>
       <c r="C2" t="n">
-        <v>4.514075944126835</v>
+        <v>6.231152678854506</v>
       </c>
       <c r="D2" t="n">
-        <v>32.12769362147687</v>
+        <v>35.55890184781947</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.8039946165159</v>
+        <v>15.27108553955914</v>
       </c>
       <c r="C3" t="n">
-        <v>25.18673735245192</v>
+        <v>23.95464398362218</v>
       </c>
       <c r="D3" t="n">
-        <v>78.74598335763666</v>
+        <v>96.1229177228052</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.41654843070368</v>
+        <v>30.29869764846506</v>
       </c>
       <c r="C4" t="n">
-        <v>60.48253081553325</v>
+        <v>79.10333952198251</v>
       </c>
       <c r="D4" t="n">
-        <v>88.22868443295661</v>
+        <v>121.5776721985165</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.36870483510285</v>
+        <v>37.23278168356029</v>
       </c>
       <c r="C5" t="n">
-        <v>104.0898003427681</v>
+        <v>141.4943878745716</v>
       </c>
       <c r="D5" t="n">
-        <v>60.40202750378502</v>
+        <v>88.77453615651784</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.37870223859457</v>
+        <v>32.96610616090365</v>
       </c>
       <c r="C6" t="n">
-        <v>105.4593383901924</v>
+        <v>154.284596965499</v>
       </c>
       <c r="D6" t="n">
-        <v>44.59883470852411</v>
+        <v>53.65545728020094</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.40432548989622</v>
+        <v>22.39759212468673</v>
       </c>
       <c r="C7" t="n">
-        <v>75.63678837828701</v>
+        <v>140.434100353985</v>
       </c>
       <c r="D7" t="n">
-        <v>39.28561613314036</v>
+        <v>40.36357511240336</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.68832831386403</v>
+        <v>11.76624623539802</v>
       </c>
       <c r="C8" t="n">
-        <v>43.39324852770901</v>
+        <v>95.46514676095984</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>35.29873870619407</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.654686850012379</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>30.7296848906294</v>
+        <v>51.03124566674919</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>29.32480392585223</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>28.42257778564941</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>33.84673385161303</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.71549845441346</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>17.45252893839555</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.722514018292781</v>
+        <v>7.630367360254522</v>
       </c>
       <c r="C21" t="n">
-        <v>96.53142522865977</v>
+        <v>92.51820424308607</v>
       </c>
       <c r="D21" t="n">
-        <v>8.687828270579379</v>
+        <v>7.630367360254522</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.03913103944963</v>
+        <v>5.477170441992955</v>
       </c>
       <c r="C2" t="n">
-        <v>9.432631942403354</v>
+        <v>7.163812997888975</v>
       </c>
       <c r="D2" t="n">
-        <v>31.60344034740907</v>
+        <v>35.08668120207675</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.26327261565417</v>
+        <v>16.64553232550467</v>
       </c>
       <c r="C3" t="n">
-        <v>20.99467465531804</v>
+        <v>23.9006478598886</v>
       </c>
       <c r="D3" t="n">
-        <v>85.11752595819847</v>
+        <v>100.270801773248</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.45934441906305</v>
+        <v>29.18834099496192</v>
       </c>
       <c r="C4" t="n">
-        <v>61.72051467058848</v>
+        <v>69.86313012961152</v>
       </c>
       <c r="D4" t="n">
-        <v>105.6753228851267</v>
+        <v>137.5948859933032</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.40016181936777</v>
+        <v>40.86524818927349</v>
       </c>
       <c r="C5" t="n">
-        <v>106.7896065294468</v>
+        <v>141.7643684932394</v>
       </c>
       <c r="D5" t="n">
-        <v>76.37997139040186</v>
+        <v>106.1023831364741</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.59004003691489</v>
+        <v>40.09064925062275</v>
       </c>
       <c r="C6" t="n">
-        <v>135.04430545767</v>
+        <v>185.680888547312</v>
       </c>
       <c r="D6" t="n">
-        <v>51.92463607761381</v>
+        <v>66.17372225705202</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.98618308334508</v>
+        <v>29.46421209985527</v>
       </c>
       <c r="C7" t="n">
-        <v>112.2873936732289</v>
+        <v>175.6474270099096</v>
       </c>
       <c r="D7" t="n">
-        <v>43.11835917051991</v>
+        <v>44.91495746929157</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.61594102565702</v>
+        <v>17.02350519163969</v>
       </c>
       <c r="C8" t="n">
-        <v>71.26506585127596</v>
+        <v>134.6859675456199</v>
       </c>
       <c r="D8" t="n">
-        <v>38.63668090063322</v>
+        <v>37.80219535202343</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.42656152972862</v>
+        <v>8.985936736971052</v>
       </c>
       <c r="C9" t="n">
-        <v>42.26718391093791</v>
+        <v>80.6515556515797</v>
       </c>
       <c r="D9" t="n">
-        <v>35.72187196672443</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>5.836490101747287</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>43.98720588877834</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.02617269731195</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.61794557879453</v>
+        <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>17.45252893839555</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.910924676973261</v>
+        <v>7.795711429962275</v>
       </c>
       <c r="C21" t="n">
-        <v>105.8086175545174</v>
+        <v>100.3697846607643</v>
       </c>
       <c r="D21" t="n">
-        <v>9.888655846216576</v>
+        <v>8.77017535870756</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.0187353218387</v>
+        <v>6.383323573012761</v>
       </c>
       <c r="C2" t="n">
-        <v>6.178138302825178</v>
+        <v>8.279078389913352</v>
       </c>
       <c r="D2" t="n">
-        <v>33.95472609908018</v>
+        <v>40.72584001527044</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.78989029575796</v>
+        <v>16.88606051304514</v>
       </c>
       <c r="C3" t="n">
-        <v>28.41177856090269</v>
+        <v>25.33890824661017</v>
       </c>
       <c r="D3" t="n">
-        <v>88.86289344990004</v>
+        <v>102.430646722591</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.69732827411827</v>
+        <v>29.31596819651401</v>
       </c>
       <c r="C4" t="n">
-        <v>56.61542660850506</v>
+        <v>64.61765214582081</v>
       </c>
       <c r="D4" t="n">
-        <v>119.2038062496477</v>
+        <v>148.6346389275586</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.62734644967627</v>
+        <v>41.55247158224626</v>
       </c>
       <c r="C5" t="n">
-        <v>109.8084807200058</v>
+        <v>134.5239791744192</v>
       </c>
       <c r="D5" t="n">
-        <v>93.53601252211487</v>
+        <v>123.1602494977624</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.43282153551517</v>
+        <v>45.60512610537709</v>
       </c>
       <c r="C6" t="n">
-        <v>149.3738949488565</v>
+        <v>202.0633124880785</v>
       </c>
       <c r="D6" t="n">
-        <v>61.26302024040947</v>
+        <v>79.77878194250432</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>48.26860762699867</v>
+        <v>36.4110588551057</v>
       </c>
       <c r="C7" t="n">
-        <v>148.4589060884984</v>
+        <v>211.2799599355475</v>
       </c>
       <c r="D7" t="n">
-        <v>47.66974152740813</v>
+        <v>50.783845245279</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>31.62700229231099</v>
+        <v>22.69800692218626</v>
       </c>
       <c r="C8" t="n">
-        <v>106.2300103380261</v>
+        <v>173.1557513365312</v>
       </c>
       <c r="D8" t="n">
-        <v>40.80634332701867</v>
+        <v>40.55599766243574</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.75156107756332</v>
+        <v>12.20312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>62.34686970589792</v>
+        <v>114.487490278446</v>
       </c>
       <c r="D9" t="n">
-        <v>37.49687181600267</v>
+        <v>35.83280945730432</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.398851609831464</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>41.14013754646259</v>
+        <v>64.34374453633596</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.686282702997524</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>35.36157055926586</v>
+        <v>39.27088991757665</v>
       </c>
       <c r="D11" t="n">
-        <v>37.31623023842126</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>31.47974013667398</v>
+        <v>29.13827186204534</v>
       </c>
       <c r="D13" t="n">
-        <v>34.08137155292803</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>17.45252893839555</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.083714597943347</v>
+        <v>7.945312440035162</v>
       </c>
       <c r="C21" t="n">
-        <v>114.1824686959498</v>
+        <v>107.2617179404747</v>
       </c>
       <c r="D21" t="n">
-        <v>11.1151075721721</v>
+        <v>9.931640550043953</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.915250902265285</v>
+        <v>5.917975161199774</v>
       </c>
       <c r="C2" t="n">
-        <v>4.101741908343174</v>
+        <v>5.827654372409066</v>
       </c>
       <c r="D2" t="n">
-        <v>27.57434776918016</v>
+        <v>33.76034005363932</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.80523840612741</v>
+        <v>19.96383956585889</v>
       </c>
       <c r="C3" t="n">
-        <v>40.04548885622739</v>
+        <v>39.26990816987242</v>
       </c>
       <c r="D3" t="n">
-        <v>96.89358967063896</v>
+        <v>110.5398827596696</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.84076124992954</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="C4" t="n">
-        <v>86.8758360965045</v>
+        <v>100.6468111439745</v>
       </c>
       <c r="D4" t="n">
-        <v>112.1077338433518</v>
+        <v>140.4792607483803</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.78408192499049</v>
+        <v>25.6727024660541</v>
       </c>
       <c r="C5" t="n">
-        <v>89.24086631603508</v>
+        <v>120.7304239297515</v>
       </c>
       <c r="D5" t="n">
-        <v>62.63550353094652</v>
+        <v>79.59519512181016</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.94723197034471</v>
+        <v>22.58117894538089</v>
       </c>
       <c r="C6" t="n">
-        <v>97.77127211823561</v>
+        <v>139.1499743568302</v>
       </c>
       <c r="D6" t="n">
-        <v>31.396291581813</v>
+        <v>33.44912603139308</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.9603134856694</v>
+        <v>15.03153909972291</v>
       </c>
       <c r="C7" t="n">
-        <v>74.67860261894212</v>
+        <v>121.7494780467597</v>
       </c>
       <c r="D7" t="n">
-        <v>28.68568617038755</v>
+        <v>28.50602634051038</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.59934912567606</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>45.89670517353839</v>
+        <v>84.36648896444964</v>
       </c>
       <c r="D8" t="n">
-        <v>27.62147165898401</v>
+        <v>26.36974333606933</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>31.39530983410874</v>
+        <v>49.03437083631118</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>27.40156017323271</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.128249096357838</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>27.75891633757857</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>29.18245050873644</v>
+        <v>28.18597658892593</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>25.58827216348886</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.07602084605028</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>27.77167905773377</v>
+        <v>26.25291535926396</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>21.853703896534</v>
       </c>
       <c r="D13" t="n">
         <v>25.49598787928967</v>
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>23.96838845148163</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>19.83915760741954</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="D18" t="n">
-        <v>14.98146996680633</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.318127313904973</v>
+        <v>3.536255230697011</v>
       </c>
       <c r="C2" t="n">
-        <v>1.860411899547706</v>
+        <v>2.709623663721197</v>
       </c>
       <c r="D2" t="n">
-        <v>19.84013935512379</v>
+        <v>23.89181213055037</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.26589906359742</v>
+        <v>20.55779692692821</v>
       </c>
       <c r="C3" t="n">
-        <v>27.91599597025805</v>
+        <v>31.77917318646925</v>
       </c>
       <c r="D3" t="n">
-        <v>97.98823836087415</v>
+        <v>111.806337298148</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.03366682604742</v>
+        <v>27.23564481121501</v>
       </c>
       <c r="C4" t="n">
-        <v>96.67760517570466</v>
+        <v>103.0589652533089</v>
       </c>
       <c r="D4" t="n">
-        <v>132.3238825692021</v>
+        <v>160.0572734664702</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.09748042682348</v>
+        <v>28.61794557879453</v>
       </c>
       <c r="C5" t="n">
-        <v>124.5346962837079</v>
+        <v>150.7964473723101</v>
       </c>
       <c r="D5" t="n">
-        <v>81.01872929296803</v>
+        <v>100.6536833779043</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.18623863083319</v>
+        <v>26.32458294167398</v>
       </c>
       <c r="C6" t="n">
-        <v>119.9901861607494</v>
+        <v>166.8833652540984</v>
       </c>
       <c r="D6" t="n">
-        <v>38.76234460677682</v>
+        <v>42.38499363544755</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.94224111636546</v>
+        <v>14.01346673041897</v>
       </c>
       <c r="C7" t="n">
-        <v>101.3281440507218</v>
+        <v>152.1119892960008</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>7.176575718044183</v>
       </c>
       <c r="C8" t="n">
-        <v>62.4195190360122</v>
+        <v>110.402438081075</v>
       </c>
       <c r="D8" t="n">
-        <v>28.87319998189869</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.104687151455913</v>
       </c>
       <c r="C9" t="n">
-        <v>37.60780930658255</v>
+        <v>51.36405813848885</v>
       </c>
       <c r="D9" t="n">
-        <v>28.95468504135117</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.18245050873644</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>30.20837685967435</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>27.98864530037232</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="D17" t="n">
-        <v>12.74995743505333</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.671155576806324</v>
+        <v>2.815652415779852</v>
       </c>
       <c r="C2" t="n">
-        <v>3.156318869153495</v>
+        <v>3.692353115672254</v>
       </c>
       <c r="D2" t="n">
-        <v>19.63593583264046</v>
+        <v>20.1150287123129</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.57176237896592</v>
+        <v>16.48354395430395</v>
       </c>
       <c r="C3" t="n">
-        <v>16.53754007803752</v>
+        <v>20.86704745376596</v>
       </c>
       <c r="D3" t="n">
-        <v>91.42034621946299</v>
+        <v>106.4067249247906</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.77987719673301</v>
+        <v>32.37902103376405</v>
       </c>
       <c r="C4" t="n">
-        <v>83.32779989335653</v>
+        <v>91.29173727020665</v>
       </c>
       <c r="D4" t="n">
-        <v>149.451453017492</v>
+        <v>173.7133840325434</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.36870483510285</v>
+        <v>33.94392687433348</v>
       </c>
       <c r="C5" t="n">
-        <v>151.3854959948582</v>
+        <v>170.4804888424586</v>
       </c>
       <c r="D5" t="n">
-        <v>106.8386939146592</v>
+        <v>129.3943474197296</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.74096714146165</v>
+        <v>31.51704654943536</v>
       </c>
       <c r="C6" t="n">
-        <v>158.7525307675263</v>
+        <v>199.2859482327643</v>
       </c>
       <c r="D6" t="n">
-        <v>52.68941753922207</v>
+        <v>59.49194738194822</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.76364514965055</v>
+        <v>20.66088043587412</v>
       </c>
       <c r="C7" t="n">
-        <v>135.2838518975062</v>
+        <v>193.0744305079947</v>
       </c>
       <c r="D7" t="n">
-        <v>34.6743471662931</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.26970288122739</v>
+        <v>9.930378028456486</v>
       </c>
       <c r="C8" t="n">
-        <v>96.13273519984767</v>
+        <v>150.207398749762</v>
       </c>
       <c r="D8" t="n">
-        <v>30.79251674370121</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>56.02343274284421</v>
+        <v>85.42186774651495</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>28.73281006019139</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>37.72365553568369</v>
+        <v>43.84485247166256</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>30.56376952861169</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>26.03594911662541</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>20.28094407433061</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>16.48354395430394</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>10.38885420633975</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.767546778271758</v>
+        <v>1.70529576227671</v>
       </c>
       <c r="C2" t="n">
-        <v>1.441205629834318</v>
+        <v>1.805434028109884</v>
       </c>
       <c r="D2" t="n">
-        <v>13.56382628187393</v>
+        <v>14.01150323501048</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.67346322958009</v>
+        <v>15.39871274111122</v>
       </c>
       <c r="C3" t="n">
-        <v>15.7128720064702</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="D3" t="n">
-        <v>89.9820858327414</v>
+        <v>103.4123944268378</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.79562621772997</v>
+        <v>35.54417563225577</v>
       </c>
       <c r="C4" t="n">
-        <v>76.44869372969913</v>
+        <v>86.77373433526283</v>
       </c>
       <c r="D4" t="n">
-        <v>160.5422568323682</v>
+        <v>186.9483248334946</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.38128762880881</v>
+        <v>34.7538687303371</v>
       </c>
       <c r="C5" t="n">
-        <v>174.3093048890212</v>
+        <v>200.7919492110789</v>
       </c>
       <c r="D5" t="n">
-        <v>116.7298020349458</v>
+        <v>135.6039016490907</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.82397372796611</v>
+        <v>25.03652995370216</v>
       </c>
       <c r="C6" t="n">
-        <v>193.6507164103876</v>
+        <v>232.8960808876539</v>
       </c>
       <c r="D6" t="n">
-        <v>51.92463607761381</v>
+        <v>57.07684802950107</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.527640485537042</v>
       </c>
       <c r="C7" t="n">
-        <v>136.7211305365236</v>
+        <v>199.841617433368</v>
       </c>
       <c r="D7" t="n">
-        <v>35.09355343600648</v>
+        <v>34.91389360612931</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>3.504839304161113</v>
       </c>
       <c r="C8" t="n">
-        <v>72.34989706446869</v>
+        <v>105.6458704539993</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>28.73281006019139</v>
+        <v>33.39218466454675</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>31.06249736236907</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.1930287493049</v>
+        <v>25.0542014123786</v>
       </c>
       <c r="D10" t="n">
-        <v>23.91537407545231</v>
+        <v>23.06125357275758</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.7904711328347</v>
+        <v>18.8358114536793</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.56743447752142</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>14.31977201414398</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>13.82791641431633</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="D16" t="n">
-        <v>9.919578803709772</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.627557767191965</v>
+        <v>2.3699389580518</v>
       </c>
       <c r="C2" t="n">
-        <v>5.862015542057704</v>
+        <v>5.08152611718149</v>
       </c>
       <c r="D2" t="n">
-        <v>10.92488845285851</v>
+        <v>13.70323445587698</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.23810702824224</v>
+        <v>10.79431600819368</v>
       </c>
       <c r="C3" t="n">
-        <v>10.38689071093125</v>
+        <v>13.40085616296896</v>
       </c>
       <c r="D3" t="n">
-        <v>80.92055452254334</v>
+        <v>92.35791527701869</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.34969177582366</v>
+        <v>32.94058072059322</v>
       </c>
       <c r="C4" t="n">
-        <v>58.15971574728529</v>
+        <v>68.71448531564275</v>
       </c>
       <c r="D4" t="n">
-        <v>167.6383292386641</v>
+        <v>193.8401937173072</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.88031856220246</v>
+        <v>42.26423866782519</v>
       </c>
       <c r="C5" t="n">
-        <v>159.7794388661684</v>
+        <v>183.8813450054276</v>
       </c>
       <c r="D5" t="n">
-        <v>142.6724851196678</v>
+        <v>163.7064296831556</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.49066253460771</v>
+        <v>32.88560284915541</v>
       </c>
       <c r="C6" t="n">
-        <v>233.5401073816398</v>
+        <v>271.9804387414237</v>
       </c>
       <c r="D6" t="n">
-        <v>71.80895407942872</v>
+        <v>79.09450379264429</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.48122060599696</v>
+        <v>13.77392029058275</v>
       </c>
       <c r="C7" t="n">
-        <v>201.6382157321396</v>
+        <v>259.7282273924234</v>
       </c>
       <c r="D7" t="n">
-        <v>40.06414206260808</v>
+        <v>40.42346172236242</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.342090169434394</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>117.6624623539802</v>
+        <v>166.8971097219577</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>32.62838495064274</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>52.02968308196819</v>
+        <v>66.78436932909349</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
         <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>24.34243432679967</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>22.21204180858408</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.45591614986479</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>14.56913593102267</v>
+      </c>
+      <c r="D13" t="n">
         <v>15.86995163914969</v>
-      </c>
-      <c r="D13" t="n">
-        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>13.82791641431633</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>24.38563122578652</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>7.852999886270235</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.550580535633213</v>
+        <v>1.54821612959722</v>
       </c>
       <c r="C2" t="n">
-        <v>3.405682786032185</v>
+        <v>3.192643534210627</v>
       </c>
       <c r="D2" t="n">
-        <v>8.223118770771283</v>
+        <v>10.45954004104552</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.7753029489145</v>
+        <v>9.748754703170828</v>
       </c>
       <c r="C3" t="n">
-        <v>16.36573422979433</v>
+        <v>16.32646432162446</v>
       </c>
       <c r="D3" t="n">
-        <v>73.3610971998429</v>
+        <v>84.80827543136071</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.168027392809</v>
+        <v>29.09900195387546</v>
       </c>
       <c r="C4" t="n">
-        <v>45.4608091928528</v>
+        <v>55.9262397201238</v>
       </c>
       <c r="D4" t="n">
-        <v>169.897330706136</v>
+        <v>195.5759236584156</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.38439710283758</v>
+        <v>46.06851102178158</v>
       </c>
       <c r="C5" t="n">
-        <v>144.6359805281614</v>
+        <v>169.228760519544</v>
       </c>
       <c r="D5" t="n">
-        <v>161.7674779672682</v>
+        <v>183.9304323906399</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.4667817945363</v>
+        <v>38.19882142453915</v>
       </c>
       <c r="C6" t="n">
-        <v>252.3376306748535</v>
+        <v>292.0660150226092</v>
       </c>
       <c r="D6" t="n">
-        <v>86.33980184998576</v>
+        <v>94.22912640131312</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.8823545064064</v>
+        <v>12.39652826152447</v>
       </c>
       <c r="C7" t="n">
-        <v>252.5418341973368</v>
+        <v>310.092866367989</v>
       </c>
       <c r="D7" t="n">
-        <v>45.21439051908685</v>
+        <v>45.63359678880023</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>3.588287859022091</v>
       </c>
       <c r="C8" t="n">
-        <v>156.2991432546135</v>
+        <v>211.2082923531376</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>63.23436963053704</v>
+        <v>73.32968127330699</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>26.05067533218912</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>21.85664913964673</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.45591614986479</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.794855787541421</v>
+        <v>1.804452280405637</v>
       </c>
       <c r="C2" t="n">
-        <v>7.35034506169587</v>
+        <v>10.48506548135594</v>
       </c>
       <c r="D2" t="n">
-        <v>14.16171063376024</v>
+        <v>9.920560551414018</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.80551614356789</v>
+        <v>7.628179661997716</v>
       </c>
       <c r="C3" t="n">
-        <v>14.74585051778709</v>
+        <v>14.42187377538564</v>
       </c>
       <c r="D3" t="n">
-        <v>65.12423396121217</v>
+        <v>76.29161409701963</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.4548365911693</v>
+        <v>24.41508365691393</v>
       </c>
       <c r="C4" t="n">
-        <v>43.22733316569131</v>
+        <v>49.18752347817369</v>
       </c>
       <c r="D4" t="n">
-        <v>166.0940400998839</v>
+        <v>191.0962088839374</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.26167863980673</v>
+        <v>45.03767593232243</v>
       </c>
       <c r="C5" t="n">
-        <v>117.4415691205247</v>
+        <v>141.4207567967531</v>
       </c>
       <c r="D5" t="n">
-        <v>180.5924901962008</v>
+        <v>204.1544350981243</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.54227855677206</v>
+        <v>46.69192081397831</v>
       </c>
       <c r="C6" t="n">
-        <v>244.0055379089108</v>
+        <v>284.2169421271559</v>
       </c>
       <c r="D6" t="n">
-        <v>109.2429940423596</v>
+        <v>118.9033914521482</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.4110588551057</v>
+        <v>22.87668500435917</v>
       </c>
       <c r="C7" t="n">
-        <v>303.0861330027795</v>
+        <v>355.0677104472396</v>
       </c>
       <c r="D7" t="n">
-        <v>55.33522760216722</v>
+        <v>56.23352675155305</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>227.1469663315845</v>
+        <v>288.8988969287089</v>
       </c>
       <c r="D8" t="n">
-        <v>38.88702656521616</v>
+        <v>36.71736413883071</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>113.3781153726471</v>
+        <v>139.0046756966016</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>47.40368789955724</v>
+        <v>48.82722207071512</v>
       </c>
       <c r="D10" t="n">
-        <v>27.61656292046278</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>12.29148125717007</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>6.091744504851459</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.015749020996954</v>
+        <v>4.370740779306799</v>
       </c>
       <c r="C2" t="n">
-        <v>2.649737053762141</v>
+        <v>12.24239387195773</v>
       </c>
       <c r="D2" t="n">
-        <v>9.371763584740052</v>
+        <v>15.28581175512284</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.392920065876976</v>
+        <v>1.304742698944011</v>
       </c>
       <c r="C2" t="n">
-        <v>4.11548637620263</v>
+        <v>6.123160431387356</v>
       </c>
       <c r="D2" t="n">
-        <v>10.42223362828414</v>
+        <v>7.38077924052752</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.53754007803752</v>
+        <v>10.25926350937917</v>
       </c>
       <c r="C3" t="n">
-        <v>21.27447275102838</v>
+        <v>23.92028281397354</v>
       </c>
       <c r="D3" t="n">
-        <v>70.73001335246146</v>
+        <v>80.95491569219199</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.43001516112266</v>
+        <v>34.10198825471721</v>
       </c>
       <c r="C4" t="n">
-        <v>64.08161789930206</v>
+        <v>73.75575977695013</v>
       </c>
       <c r="D4" t="n">
-        <v>171.5181961658475</v>
+        <v>196.0864324646239</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.44800541496859</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="C5" t="n">
-        <v>191.5144334059466</v>
+        <v>228.5263218560513</v>
       </c>
       <c r="D5" t="n">
-        <v>164.3936530761284</v>
+        <v>183.218665305061</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.58117894538089</v>
+        <v>14.16858286768997</v>
       </c>
       <c r="C6" t="n">
-        <v>252.2168757072311</v>
+        <v>286.7930481030995</v>
       </c>
       <c r="D6" t="n">
-        <v>84.85049058264335</v>
+        <v>89.31842438467058</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.827073535332318</v>
+        <v>4.251949307092936</v>
       </c>
       <c r="C7" t="n">
-        <v>159.7175887608009</v>
+        <v>203.135380981116</v>
       </c>
       <c r="D7" t="n">
-        <v>34.91389360612931</v>
+        <v>32.93763547748049</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>1.418625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>83.53200341583985</v>
+        <v>102.3913768144211</v>
       </c>
       <c r="D8" t="n">
-        <v>25.2849121228766</v>
+        <v>23.86628669023996</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>36.16562192904399</v>
+        <v>37.27499683484289</v>
       </c>
       <c r="D9" t="n">
-        <v>21.07812321017901</v>
+        <v>19.85781081380023</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.49183990429443</v>
+        <v>20.4988920646734</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>18.79065105928395</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.8811517745239</v>
+        <v>14.74879576089983</v>
       </c>
       <c r="D11" t="n">
-        <v>16.8811517745239</v>
+        <v>15.99267010218054</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>10.14636252339079</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.53116656572653</v>
+        <v>4.916592502868027</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.005751617505239</v>
+        <v>5.844344083381262</v>
       </c>
       <c r="C2" t="n">
-        <v>4.146902302738527</v>
+        <v>8.2486442110817</v>
       </c>
       <c r="D2" t="n">
-        <v>13.01797455831271</v>
+        <v>25.47537117750048</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.65687132959913</v>
+        <v>9.29224202069606</v>
       </c>
       <c r="C3" t="n">
-        <v>6.778967897824225</v>
+        <v>30.84651286743478</v>
       </c>
       <c r="D3" t="n">
-        <v>11.38336463074177</v>
+        <v>15.97794388661684</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39907842552735</v>
+        <v>13.3965285559105</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14811646305498</v>
+        <v>70.13476714564911</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576362167709101</v>
+        <v>1.576062183048294</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.362886797672825</v>
+        <v>3.769911184307752</v>
       </c>
       <c r="C2" t="n">
-        <v>3.229949946972006</v>
+        <v>4.663301595172349</v>
       </c>
       <c r="D2" t="n">
-        <v>16.2665777116654</v>
+        <v>33.91054745238908</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.73665493555038</v>
+        <v>15.80122929985241</v>
       </c>
       <c r="C3" t="n">
-        <v>12.75290267816607</v>
+        <v>31.6711809390021</v>
       </c>
       <c r="D3" t="n">
-        <v>19.56623174563893</v>
+        <v>33.51686662298611</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.45641487148353</v>
+        <v>10.92488845285851</v>
       </c>
       <c r="C4" t="n">
-        <v>11.03975293425538</v>
+        <v>47.54113257815179</v>
       </c>
       <c r="D4" t="n">
-        <v>21.03296281578367</v>
+        <v>23.44511692511808</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.117048960983624</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.07441720354028</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>25.36836067773758</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.96770980341364</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>39.82655911818034</v>
       </c>
     </row>
     <row r="10">
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4980,10 +4980,10 @@
         <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>26.53664044579129</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44535700171343</v>
+        <v>15.43446986836818</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16883379903281</v>
+        <v>86.10809505510667</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251654105623879</v>
+        <v>3.249362077551195</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.703553251046468</v>
+        <v>4.474806035956962</v>
       </c>
       <c r="C2" t="n">
-        <v>9.729119749085891</v>
+        <v>9.040914608408876</v>
       </c>
       <c r="D2" t="n">
-        <v>15.620587722271</v>
+        <v>38.98029259711961</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.70443718775948</v>
+        <v>14.23534171157875</v>
       </c>
       <c r="C3" t="n">
-        <v>12.64491043069892</v>
+        <v>23.58648859452962</v>
       </c>
       <c r="D3" t="n">
-        <v>28.0387144332889</v>
+        <v>52.86711387369073</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.26567807941916</v>
+        <v>21.72214970416493</v>
       </c>
       <c r="C4" t="n">
-        <v>23.54721868635975</v>
+        <v>65.91944960165209</v>
       </c>
       <c r="D4" t="n">
-        <v>25.90832191507333</v>
+        <v>34.95709050511617</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.29009859883832</v>
+        <v>9.989282890711298</v>
       </c>
       <c r="C5" t="n">
-        <v>14.08807955594173</v>
+        <v>51.56629816556373</v>
       </c>
       <c r="D5" t="n">
-        <v>30.38509144643879</v>
+        <v>31.3668391506856</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.10573531908495</v>
       </c>
     </row>
     <row r="7">
@@ -5210,7 +5210,7 @@
         <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>40.82499653339935</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
-        <v>49.82369599052563</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>49.04418831335365</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5305,10 +5305,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>31.56809743005619</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74612498120033</v>
+        <v>16.71806670766131</v>
       </c>
       <c r="C21" t="n">
-        <v>102.151362385322</v>
+        <v>101.1443035813509</v>
       </c>
       <c r="D21" t="n">
-        <v>5.0238374943601</v>
+        <v>4.179516676915327</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.15221195188726</v>
+        <v>5.266094685579891</v>
       </c>
       <c r="C2" t="n">
-        <v>6.319509972236719</v>
+        <v>11.50510134606837</v>
       </c>
       <c r="D2" t="n">
-        <v>23.14077513680157</v>
+        <v>29.73517446622739</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.42954783057037</v>
+        <v>14.72130682518092</v>
       </c>
       <c r="C3" t="n">
-        <v>27.40057842552848</v>
+        <v>30.3016428915778</v>
       </c>
       <c r="D3" t="n">
-        <v>33.6739462556656</v>
+        <v>69.67954330891737</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.83923972287755</v>
+        <v>24.54271085846601</v>
       </c>
       <c r="C4" t="n">
-        <v>28.15456066239003</v>
+        <v>61.52907386826035</v>
       </c>
       <c r="D4" t="n">
-        <v>33.43832680664636</v>
+        <v>51.26784686347268</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.52544031041707</v>
+        <v>20.91122610045706</v>
       </c>
       <c r="C5" t="n">
-        <v>30.11511082777092</v>
+        <v>88.74999246391167</v>
       </c>
       <c r="D5" t="n">
-        <v>32.98672286269284</v>
+        <v>36.59464567579986</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.78744377426395</v>
+        <v>9.700649065662736</v>
       </c>
       <c r="C6" t="n">
-        <v>17.71072858461246</v>
+        <v>47.41645061971246</v>
       </c>
       <c r="D6" t="n">
-        <v>38.03781480104267</v>
+        <v>37.75605320992383</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>21.25974653546468</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
         <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.55461500410399</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.50155957034565</v>
+        <v>33.61405964570653</v>
       </c>
       <c r="D9" t="n">
-        <v>41.60155896745857</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>48.9695754878309</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.28806265463436</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.51560713784138</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
       <c r="D14" t="n">
         <v>45.7857676829585</v>
@@ -5633,7 +5633,7 @@
         <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5675,7 +5675,7 @@
         <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5686,7 +5686,7 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.91411459030757</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>25.27607639353838</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.08407087722541</v>
+        <v>18.02723241353186</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9770338180896</v>
+        <v>116.7477908685873</v>
       </c>
       <c r="D21" t="n">
-        <v>6.889169857990632</v>
+        <v>6.009077471177287</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.165375582669969</v>
+        <v>5.633268326968198</v>
       </c>
       <c r="C2" t="n">
-        <v>8.159305169995241</v>
+        <v>10.59109423341459</v>
       </c>
       <c r="D2" t="n">
-        <v>30.6707800283746</v>
+        <v>28.45301196448106</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.32017292477148</v>
+        <v>14.66240196292611</v>
       </c>
       <c r="C3" t="n">
-        <v>24.21971586376881</v>
+        <v>35.82397372796611</v>
       </c>
       <c r="D3" t="n">
-        <v>41.17449871611123</v>
+        <v>71.68230862558086</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.50067563363265</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="C4" t="n">
-        <v>42.70406163932775</v>
+        <v>57.30461349688632</v>
       </c>
       <c r="D4" t="n">
-        <v>36.60348140513808</v>
+        <v>62.47351515974578</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.91751749731004</v>
+        <v>17.42602175038089</v>
       </c>
       <c r="C5" t="n">
-        <v>31.48955761371645</v>
+        <v>75.59457322700442</v>
       </c>
       <c r="D5" t="n">
-        <v>30.55689729468198</v>
+        <v>37.40458753180348</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.47801332097696</v>
+        <v>10.18366893615217</v>
       </c>
       <c r="C6" t="n">
-        <v>22.78243722475149</v>
+        <v>63.59761628110839</v>
       </c>
       <c r="D6" t="n">
-        <v>30.71201343195298</v>
+        <v>31.15478164656829</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.449681506274044</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>15.21119892960008</v>
+        <v>28.62579956042849</v>
       </c>
       <c r="D7" t="n">
-        <v>31.4404702285041</v>
+        <v>31.08115056874977</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>29.45733986592554</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>21.52187317249857</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
         <v>30.17892442854696</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.073333530670975</v>
+        <v>7.038501022153874</v>
       </c>
       <c r="C21" t="n">
-        <v>67.19666854137427</v>
+        <v>65.98594708269256</v>
       </c>
       <c r="D21" t="n">
-        <v>5.305000148003232</v>
+        <v>4.399063138846171</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.285729639664827</v>
+        <v>4.263730279543897</v>
       </c>
       <c r="C2" t="n">
-        <v>4.673119072214817</v>
+        <v>5.378995671568275</v>
       </c>
       <c r="D2" t="n">
-        <v>32.98672286269283</v>
+        <v>38.86837335883547</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.32079481957723</v>
+        <v>17.61255381418778</v>
       </c>
       <c r="C3" t="n">
-        <v>29.3493476184584</v>
+        <v>39.25027321578748</v>
       </c>
       <c r="D3" t="n">
-        <v>57.82003104161589</v>
+        <v>78.26001824403448</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.5164246546296</v>
+        <v>24.9766433437431</v>
       </c>
       <c r="C4" t="n">
-        <v>54.45852690227482</v>
+        <v>77.08682973745954</v>
       </c>
       <c r="D4" t="n">
-        <v>50.36169373245288</v>
+        <v>85.54851320036282</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.08427573831176</v>
+        <v>23.90555659840983</v>
       </c>
       <c r="C5" t="n">
-        <v>61.45740628585034</v>
+        <v>93.60964359993338</v>
       </c>
       <c r="D5" t="n">
-        <v>37.35550014659114</v>
+        <v>52.13080309550564</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.78243722475149</v>
+        <v>17.75098024048658</v>
       </c>
       <c r="C6" t="n">
-        <v>39.36611944488861</v>
+        <v>95.2354177981661</v>
       </c>
       <c r="D6" t="n">
-        <v>34.17365583712723</v>
+        <v>35.90447703971436</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.0191362324662</v>
+        <v>8.982991493858314</v>
       </c>
       <c r="C7" t="n">
-        <v>25.99078872223005</v>
+        <v>64.79731197569798</v>
       </c>
       <c r="D7" t="n">
-        <v>33.89582123682538</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>19.94420461177395</v>
+        <v>29.79113408536946</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.07499804061703</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>25.0542014123786</v>
+        <v>24.20008090968388</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>34.82848155585983</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.302273195091405</v>
+        <v>7.251449203144393</v>
       </c>
       <c r="C21" t="n">
-        <v>77.58665269784618</v>
+        <v>75.23378548262309</v>
       </c>
       <c r="D21" t="n">
-        <v>6.38948904570498</v>
+        <v>5.438586902358295</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.905793278121311</v>
+        <v>4.372704274715294</v>
       </c>
       <c r="C2" t="n">
-        <v>7.022441328477434</v>
+        <v>5.14337622254904</v>
       </c>
       <c r="D2" t="n">
-        <v>30.40472640052372</v>
+        <v>35.4420738710141</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.01154429273948</v>
+        <v>15.96812640957437</v>
       </c>
       <c r="C3" t="n">
-        <v>22.38875639534851</v>
+        <v>28.62776305583699</v>
       </c>
       <c r="D3" t="n">
-        <v>71.55468142402877</v>
+        <v>90.39441986852506</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.3489877655599</v>
+        <v>30.03068052520568</v>
       </c>
       <c r="C4" t="n">
-        <v>66.11089040398021</v>
+        <v>88.89234588102745</v>
       </c>
       <c r="D4" t="n">
-        <v>68.98250243890213</v>
+        <v>104.4501017502267</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.32466505713199</v>
+        <v>30.77779052813751</v>
       </c>
       <c r="C5" t="n">
-        <v>84.6757394912874</v>
+        <v>119.0859965251381</v>
       </c>
       <c r="D5" t="n">
-        <v>47.63930734857648</v>
+        <v>69.45865007546185</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.08056973167303</v>
+        <v>25.43904651244335</v>
       </c>
       <c r="C6" t="n">
-        <v>72.49323222928874</v>
+        <v>123.8140934687908</v>
       </c>
       <c r="D6" t="n">
-        <v>38.27932473628739</v>
+        <v>43.9548082145382</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.06201433628357</v>
+        <v>15.09142570968197</v>
       </c>
       <c r="C7" t="n">
-        <v>43.5375654402333</v>
+        <v>103.1846289594525</v>
       </c>
       <c r="D7" t="n">
-        <v>36.65060529494193</v>
+        <v>36.17151241526948</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.179341034707678</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>28.12216298814988</v>
+        <v>58.4974369575462</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>33.54631905411351</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>24.84999788989526</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>25.58827216348886</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>33.41280136633594</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>17.45252893839555</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.519274652238462</v>
+        <v>7.448822931783596</v>
       </c>
       <c r="C21" t="n">
-        <v>87.41156783227211</v>
+        <v>83.79925798256545</v>
       </c>
       <c r="D21" t="n">
-        <v>7.519274652238462</v>
+        <v>6.517720065310646</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_38_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_38_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497635273064</v>
+        <v>10.84497631695651</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907201339558</v>
+        <v>37.78907188874143</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.584180941755857</v>
+        <v>4.979424355939822</v>
       </c>
       <c r="C2" t="n">
-        <v>6.231152678854506</v>
+        <v>9.291260272991813</v>
       </c>
       <c r="D2" t="n">
-        <v>35.55890184781947</v>
+        <v>18.57957530287089</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.27108553955914</v>
+        <v>16.06139244147782</v>
       </c>
       <c r="C3" t="n">
-        <v>23.95464398362218</v>
+        <v>29.66350688381738</v>
       </c>
       <c r="D3" t="n">
-        <v>96.1229177228052</v>
+        <v>56.28850462299088</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.29869764846506</v>
+        <v>31.84298678724529</v>
       </c>
       <c r="C4" t="n">
-        <v>79.10333952198251</v>
+        <v>83.36608805382215</v>
       </c>
       <c r="D4" t="n">
-        <v>121.5776721985165</v>
+        <v>63.90293981712914</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.23278168356029</v>
+        <v>38.97538385859838</v>
       </c>
       <c r="C5" t="n">
-        <v>141.4943878745716</v>
+        <v>116.0180349493668</v>
       </c>
       <c r="D5" t="n">
-        <v>88.77453615651784</v>
+        <v>48.05655012288138</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.96610616090365</v>
+        <v>38.31957639216151</v>
       </c>
       <c r="C6" t="n">
-        <v>154.284596965499</v>
+        <v>108.719722515996</v>
       </c>
       <c r="D6" t="n">
-        <v>53.65545728020094</v>
+        <v>40.01014593887452</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.39759212468673</v>
+        <v>28.20659329071511</v>
       </c>
       <c r="C7" t="n">
-        <v>140.434100353985</v>
+        <v>97.37562779342413</v>
       </c>
       <c r="D7" t="n">
-        <v>40.36357511240336</v>
+        <v>38.20765715387736</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.76624623539802</v>
+        <v>15.60487975900305</v>
       </c>
       <c r="C8" t="n">
-        <v>95.46514676095984</v>
+        <v>72.43334561932966</v>
       </c>
       <c r="D8" t="n">
-        <v>35.29873870619407</v>
+        <v>36.55046702910875</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>51.03124566674919</v>
+        <v>44.81874619427537</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>34.50155957034565</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.25371718051895</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>26.90381408717959</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.71549845441346</v>
+        <v>26.27647730416588</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.630367360254522</v>
+        <v>7.713771790186439</v>
       </c>
       <c r="C21" t="n">
-        <v>92.51820424308607</v>
+        <v>96.42214737733049</v>
       </c>
       <c r="D21" t="n">
-        <v>7.630367360254522</v>
+        <v>8.677993263959744</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.477170441992955</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C2" t="n">
-        <v>7.163812997888975</v>
+        <v>10.48212023824319</v>
       </c>
       <c r="D2" t="n">
-        <v>35.08668120207675</v>
+        <v>16.59939018340507</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.64553232550467</v>
+        <v>16.3608254912731</v>
       </c>
       <c r="C3" t="n">
-        <v>23.9006478598886</v>
+        <v>32.90327430783185</v>
       </c>
       <c r="D3" t="n">
-        <v>100.270801773248</v>
+        <v>57.48132808365075</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.18834099496192</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="C4" t="n">
-        <v>69.86313012961152</v>
+        <v>77.77601662584082</v>
       </c>
       <c r="D4" t="n">
-        <v>137.5948859933032</v>
+        <v>74.78954010952202</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.86524818927349</v>
+        <v>42.97600575340413</v>
       </c>
       <c r="C5" t="n">
-        <v>141.7643684932394</v>
+        <v>134.8675908709056</v>
       </c>
       <c r="D5" t="n">
-        <v>106.1023831364741</v>
+        <v>58.80668748438396</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.09064925062275</v>
+        <v>45.2026095466359</v>
       </c>
       <c r="C6" t="n">
-        <v>185.680888547312</v>
+        <v>144.141179685221</v>
       </c>
       <c r="D6" t="n">
-        <v>66.17372225705202</v>
+        <v>45.04160292313942</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.46421209985527</v>
+        <v>36.9500383447372</v>
       </c>
       <c r="C7" t="n">
-        <v>175.6474270099096</v>
+        <v>126.9596131131975</v>
       </c>
       <c r="D7" t="n">
-        <v>44.91495746929157</v>
+        <v>41.14210104187108</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.02350519163969</v>
+        <v>22.61455836732527</v>
       </c>
       <c r="C8" t="n">
-        <v>134.6859675456199</v>
+        <v>99.5541259491478</v>
       </c>
       <c r="D8" t="n">
-        <v>37.80219535202343</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.985936736971052</v>
+        <v>11.53749902030851</v>
       </c>
       <c r="C9" t="n">
-        <v>80.6515556515797</v>
+        <v>66.89530681967339</v>
       </c>
       <c r="D9" t="n">
-        <v>34.72343455150543</v>
+        <v>36.16562192904399</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.836490101747287</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>43.98720588877834</v>
+        <v>41.99425804915732</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>28.87810872041993</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.795711429962275</v>
+        <v>7.900481876489169</v>
       </c>
       <c r="C21" t="n">
-        <v>100.3697846607643</v>
+        <v>105.6689450980426</v>
       </c>
       <c r="D21" t="n">
-        <v>8.77017535870756</v>
+        <v>9.875602345611462</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.383323573012761</v>
+        <v>8.896597695884596</v>
       </c>
       <c r="C2" t="n">
-        <v>8.279078389913352</v>
+        <v>15.59702577736908</v>
       </c>
       <c r="D2" t="n">
-        <v>40.72584001527044</v>
+        <v>21.19004244846316</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.88606051304514</v>
+        <v>20.08655802888974</v>
       </c>
       <c r="C3" t="n">
-        <v>25.33890824661017</v>
+        <v>36.44738352016284</v>
       </c>
       <c r="D3" t="n">
-        <v>102.430646722591</v>
+        <v>56.97572801596364</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.31596819651401</v>
+        <v>30.6560538128109</v>
       </c>
       <c r="C4" t="n">
-        <v>64.61765214582081</v>
+        <v>79.66489920881168</v>
       </c>
       <c r="D4" t="n">
-        <v>148.6346389275586</v>
+        <v>83.97869862127216</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.55247158224626</v>
+        <v>44.49771469498668</v>
       </c>
       <c r="C5" t="n">
-        <v>134.5239791744192</v>
+        <v>137.1010668980671</v>
       </c>
       <c r="D5" t="n">
-        <v>123.1602494977624</v>
+        <v>68.6732519120644</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.60512610537709</v>
+        <v>51.24035792775378</v>
       </c>
       <c r="C6" t="n">
-        <v>202.0633124880785</v>
+        <v>173.9274050320692</v>
       </c>
       <c r="D6" t="n">
-        <v>79.77878194250432</v>
+        <v>51.84413276586557</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.4110588551057</v>
+        <v>44.25620475974196</v>
       </c>
       <c r="C7" t="n">
-        <v>211.2799599355475</v>
+        <v>163.7299916280575</v>
       </c>
       <c r="D7" t="n">
-        <v>50.783845245279</v>
+        <v>43.83699849002857</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.69800692218626</v>
+        <v>30.12492830481337</v>
       </c>
       <c r="C8" t="n">
-        <v>173.1557513365312</v>
+        <v>129.5956056991002</v>
       </c>
       <c r="D8" t="n">
-        <v>40.55599766243574</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.20312396378785</v>
+        <v>16.30781111524376</v>
       </c>
       <c r="C9" t="n">
-        <v>114.487490278446</v>
+        <v>92.52186714362787</v>
       </c>
       <c r="D9" t="n">
-        <v>35.83280945730432</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.8329640215578</v>
+        <v>8.541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>64.34374453633596</v>
+        <v>57.79548734900973</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>36.15776794741003</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>39.27088991757665</v>
+        <v>40.15937158992001</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>37.31623023842126</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.13827186204534</v>
+        <v>31.21957699504857</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>33.82120841130262</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>19.25796296650543</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.945312440035162</v>
+        <v>8.07135184433297</v>
       </c>
       <c r="C21" t="n">
-        <v>107.2617179404747</v>
+        <v>114.0078448012032</v>
       </c>
       <c r="D21" t="n">
-        <v>9.931640550043953</v>
+        <v>11.09810878595783</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.917975161199774</v>
+        <v>7.981608835526568</v>
       </c>
       <c r="C2" t="n">
-        <v>5.827654372409066</v>
+        <v>10.48113849053895</v>
       </c>
       <c r="D2" t="n">
-        <v>33.76034005363932</v>
+        <v>17.38871533761951</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.96383956585889</v>
+        <v>22.87963024747192</v>
       </c>
       <c r="C3" t="n">
-        <v>39.26990816987242</v>
+        <v>57.02972413969722</v>
       </c>
       <c r="D3" t="n">
-        <v>110.5398827596696</v>
+        <v>62.12008598621694</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.96089432274615</v>
+        <v>21.3775562599743</v>
       </c>
       <c r="C4" t="n">
-        <v>100.6468111439745</v>
+        <v>113.5626839410455</v>
       </c>
       <c r="D4" t="n">
-        <v>140.4792607483803</v>
+        <v>79.95844177238148</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.6727024660541</v>
+        <v>28.86338250485623</v>
       </c>
       <c r="C5" t="n">
-        <v>120.7304239297515</v>
+        <v>103.9179944945249</v>
       </c>
       <c r="D5" t="n">
-        <v>79.59519512181016</v>
+        <v>50.09367660919352</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.58117894538089</v>
+        <v>27.45162930614931</v>
       </c>
       <c r="C6" t="n">
-        <v>139.1499743568302</v>
+        <v>107.8341860867654</v>
       </c>
       <c r="D6" t="n">
-        <v>33.44912603139308</v>
+        <v>28.86043726174349</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.03153909972291</v>
+        <v>19.94224111636546</v>
       </c>
       <c r="C7" t="n">
-        <v>121.7494780467597</v>
+        <v>91.0875337477233</v>
       </c>
       <c r="D7" t="n">
-        <v>28.50602634051038</v>
+        <v>28.14670668075605</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>11.26555490623215</v>
       </c>
       <c r="C8" t="n">
-        <v>84.36648896444964</v>
+        <v>68.17746932141974</v>
       </c>
       <c r="D8" t="n">
-        <v>26.36974333606933</v>
+        <v>27.78836876870596</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>49.03437083631118</v>
+        <v>44.04218376021615</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>27.5124976638126</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>28.18597658892593</v>
+        <v>29.18245050873644</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>25.58827216348886</v>
+        <v>27.36523550817559</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>28.25371718051895</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>23.64932044760141</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>26.25291535926396</v>
+        <v>27.55471281509523</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
         <v>25.49598787928967</v>
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>16.58662746324986</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.536255230697011</v>
+        <v>4.688827035482766</v>
       </c>
       <c r="C2" t="n">
-        <v>2.709623663721197</v>
+        <v>5.043237956715865</v>
       </c>
       <c r="D2" t="n">
-        <v>23.89181213055037</v>
+        <v>12.19036124363264</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.55779692692821</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="C3" t="n">
-        <v>31.77917318646925</v>
+        <v>49.72061248157971</v>
       </c>
       <c r="D3" t="n">
-        <v>111.806337298148</v>
+        <v>61.9139189683251</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.23564481121501</v>
+        <v>31.20485077948487</v>
       </c>
       <c r="C4" t="n">
-        <v>103.0589652533089</v>
+        <v>130.7923561505771</v>
       </c>
       <c r="D4" t="n">
-        <v>160.0572734664702</v>
+        <v>91.58527983377644</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.61794557879453</v>
+        <v>32.0295188510522</v>
       </c>
       <c r="C5" t="n">
-        <v>150.7964473723101</v>
+        <v>155.0915935783899</v>
       </c>
       <c r="D5" t="n">
-        <v>100.6536833779043</v>
+        <v>62.46369768270332</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.32458294167398</v>
+        <v>32.8453511932813</v>
       </c>
       <c r="C6" t="n">
-        <v>166.8833652540984</v>
+        <v>136.6141200367607</v>
       </c>
       <c r="D6" t="n">
-        <v>42.38499363544755</v>
+        <v>34.45541742824607</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.01346673041897</v>
+        <v>18.86428213710246</v>
       </c>
       <c r="C7" t="n">
-        <v>152.1119892960008</v>
+        <v>117.1980956898715</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>30.60205768907732</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.176575718044183</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>110.402438081075</v>
+        <v>88.78926237208152</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>28.95664853675967</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.104687151455913</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>51.36405813848885</v>
+        <v>50.14374574211007</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>29.18245050873644</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.07602084605028</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>27.98864530037232</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.70599977254047</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.815652415779852</v>
+        <v>5.109015052900402</v>
       </c>
       <c r="C2" t="n">
-        <v>3.692353115672254</v>
+        <v>7.133378819057324</v>
       </c>
       <c r="D2" t="n">
-        <v>20.1150287123129</v>
+        <v>15.09044396197772</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.48354395430395</v>
+        <v>20.78850763742621</v>
       </c>
       <c r="C3" t="n">
-        <v>20.86704745376596</v>
+        <v>33.60031517784709</v>
       </c>
       <c r="D3" t="n">
-        <v>106.4067249247906</v>
+        <v>58.10964661436871</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.37902103376405</v>
+        <v>40.17704304859647</v>
       </c>
       <c r="C4" t="n">
-        <v>91.29173727020665</v>
+        <v>127.3081335482051</v>
       </c>
       <c r="D4" t="n">
-        <v>173.7133840325434</v>
+        <v>99.24291192690157</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.94392687433348</v>
+        <v>38.8772090881737</v>
       </c>
       <c r="C5" t="n">
-        <v>170.4804888424586</v>
+        <v>199.6383956585889</v>
       </c>
       <c r="D5" t="n">
-        <v>129.3943474197296</v>
+        <v>79.10432126968676</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.51704654943536</v>
+        <v>37.79630486579796</v>
       </c>
       <c r="C6" t="n">
-        <v>199.2859482327643</v>
+        <v>188.377749490878</v>
       </c>
       <c r="D6" t="n">
-        <v>59.49194738194822</v>
+        <v>44.39757642915352</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.66088043587412</v>
+        <v>27.24840753137022</v>
       </c>
       <c r="C7" t="n">
-        <v>193.0744305079947</v>
+        <v>156.2441653831756</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.930378028456486</v>
+        <v>13.68556299720053</v>
       </c>
       <c r="C8" t="n">
-        <v>150.207398749762</v>
+        <v>120.2493675546706</v>
       </c>
       <c r="D8" t="n">
-        <v>29.12354564648163</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>6.545311944213482</v>
       </c>
       <c r="C9" t="n">
-        <v>85.42186774651495</v>
+        <v>76.54686850012379</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>29.39843500367073</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>43.84485247166256</v>
+        <v>45.26838664282043</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.7483380970101</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>34.65078522139116</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>23.64932044760141</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.69109363052753</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.79680358741669</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.97365704290136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>16.48354395430394</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.70529576227671</v>
+        <v>3.00709321810798</v>
       </c>
       <c r="C2" t="n">
-        <v>1.805434028109884</v>
+        <v>3.329106465100934</v>
       </c>
       <c r="D2" t="n">
-        <v>14.01150323501048</v>
+        <v>10.52335364182156</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.39871274111122</v>
+        <v>21.15666302651876</v>
       </c>
       <c r="C3" t="n">
-        <v>19.52696183746906</v>
+        <v>32.94745295452295</v>
       </c>
       <c r="D3" t="n">
-        <v>103.4123944268378</v>
+        <v>58.61033794353458</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.54417563225577</v>
+        <v>44.4015034199705</v>
       </c>
       <c r="C4" t="n">
-        <v>86.77373433526283</v>
+        <v>124.6790131962322</v>
       </c>
       <c r="D4" t="n">
-        <v>186.9483248334946</v>
+        <v>105.8540009672996</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.7538687303371</v>
+        <v>40.64435495581795</v>
       </c>
       <c r="C5" t="n">
-        <v>200.7919492110789</v>
+        <v>237.4847696573035</v>
       </c>
       <c r="D5" t="n">
-        <v>135.6039016490907</v>
+        <v>83.57127332400975</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.03652995370216</v>
+        <v>32.28182801104362</v>
       </c>
       <c r="C6" t="n">
-        <v>232.8960808876539</v>
+        <v>227.1400940976548</v>
       </c>
       <c r="D6" t="n">
-        <v>57.07684802950107</v>
+        <v>44.23656980565704</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.527640485537042</v>
+        <v>9.042878103817369</v>
       </c>
       <c r="C7" t="n">
-        <v>199.841617433368</v>
+        <v>161.5740736695315</v>
       </c>
       <c r="D7" t="n">
-        <v>34.91389360612931</v>
+        <v>34.07548106670254</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.504839304161113</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>105.6458704539993</v>
+        <v>94.12996988318417</v>
       </c>
       <c r="D8" t="n">
-        <v>30.79251674370121</v>
+        <v>31.79389940203295</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>33.39218466454675</v>
+        <v>34.50155957034565</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.0542014123786</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>23.06125357275758</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>18.8358114536793</v>
+        <v>21.32356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>22.56743447752142</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.31977201414398</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.90016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.3699389580518</v>
+        <v>3.377212102609028</v>
       </c>
       <c r="C2" t="n">
-        <v>5.08152611718149</v>
+        <v>3.311435006424491</v>
       </c>
       <c r="D2" t="n">
-        <v>13.70323445587698</v>
+        <v>13.33017032826319</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.79431600819368</v>
+        <v>15.92394776288327</v>
       </c>
       <c r="C3" t="n">
-        <v>13.40085616296896</v>
+        <v>22.78636421556847</v>
       </c>
       <c r="D3" t="n">
-        <v>92.35791527701869</v>
+        <v>53.85377031645879</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.94058072059322</v>
+        <v>42.48709539668921</v>
       </c>
       <c r="C4" t="n">
-        <v>68.71448531564275</v>
+        <v>103.7226267013798</v>
       </c>
       <c r="D4" t="n">
-        <v>193.8401937173072</v>
+        <v>111.2398688727976</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.26423866782519</v>
+        <v>51.71356032120075</v>
       </c>
       <c r="C5" t="n">
-        <v>183.8813450054276</v>
+        <v>235.8403422526901</v>
       </c>
       <c r="D5" t="n">
-        <v>163.7064296831556</v>
+        <v>98.29748888771192</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.88560284915541</v>
+        <v>41.45920555034281</v>
       </c>
       <c r="C6" t="n">
-        <v>271.9804387414237</v>
+        <v>295.8094190189022</v>
       </c>
       <c r="D6" t="n">
-        <v>79.09450379264429</v>
+        <v>56.11080828852221</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.77392029058275</v>
+        <v>18.44507586738907</v>
       </c>
       <c r="C7" t="n">
-        <v>259.7282273924234</v>
+        <v>235.534036968965</v>
       </c>
       <c r="D7" t="n">
-        <v>40.42346172236242</v>
+        <v>38.08788393395925</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>166.8971097219577</v>
+        <v>143.3646172511617</v>
       </c>
       <c r="D8" t="n">
-        <v>32.62838495064274</v>
+        <v>33.46287049925253</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>66.78436932909349</v>
+        <v>64.78749449865549</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>24.34243432679967</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>22.21204180858408</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.56913593102267</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.54821612959722</v>
+        <v>2.428843820306609</v>
       </c>
       <c r="C2" t="n">
-        <v>3.192643534210627</v>
+        <v>2.752820562708056</v>
       </c>
       <c r="D2" t="n">
-        <v>10.45954004104552</v>
+        <v>10.34369381194439</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.748754703170828</v>
+        <v>14.22061549601505</v>
       </c>
       <c r="C3" t="n">
-        <v>16.32646432162446</v>
+        <v>18.64338890364693</v>
       </c>
       <c r="D3" t="n">
-        <v>84.80827543136071</v>
+        <v>52.45968857642831</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.09900195387546</v>
+        <v>38.81143199198916</v>
       </c>
       <c r="C4" t="n">
-        <v>55.9262397201238</v>
+        <v>86.60781897324512</v>
       </c>
       <c r="D4" t="n">
-        <v>195.5759236584156</v>
+        <v>113.8562265046153</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.06851102178158</v>
+        <v>56.8677357684965</v>
       </c>
       <c r="C5" t="n">
-        <v>169.228760519544</v>
+        <v>224.7956805799135</v>
       </c>
       <c r="D5" t="n">
-        <v>183.9304323906399</v>
+        <v>108.4585776266664</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.19882142453915</v>
+        <v>49.3887817575443</v>
       </c>
       <c r="C6" t="n">
-        <v>292.0660150226092</v>
+        <v>336.222081516518</v>
       </c>
       <c r="D6" t="n">
-        <v>94.22912640131312</v>
+        <v>66.1334706011779</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.39652826152447</v>
+        <v>16.76825078853552</v>
       </c>
       <c r="C7" t="n">
-        <v>310.092866367989</v>
+        <v>301.7087409737213</v>
       </c>
       <c r="D7" t="n">
-        <v>45.63359678880023</v>
+        <v>41.74096714146164</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.588287859022091</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>211.2082923531376</v>
+        <v>187.2585571080366</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>34.46425315758427</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>73.32968127330699</v>
+        <v>75.10468112258522</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>21.85664913964673</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.804452280405637</v>
+        <v>3.386047831947249</v>
       </c>
       <c r="C2" t="n">
-        <v>10.48506548135594</v>
+        <v>6.522731747015809</v>
       </c>
       <c r="D2" t="n">
-        <v>9.920560551414018</v>
+        <v>11.08785857176348</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.628179661997716</v>
+        <v>11.25082869066845</v>
       </c>
       <c r="C3" t="n">
-        <v>14.42187377538564</v>
+        <v>14.86366024229671</v>
       </c>
       <c r="D3" t="n">
-        <v>76.29161409701963</v>
+        <v>49.00884539600077</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.41508365691393</v>
+        <v>33.48937768726719</v>
       </c>
       <c r="C4" t="n">
-        <v>49.18752347817369</v>
+        <v>68.68895987533233</v>
       </c>
       <c r="D4" t="n">
-        <v>191.0962088839374</v>
+        <v>113.6392602619768</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.03767593232243</v>
+        <v>57.23589115758906</v>
       </c>
       <c r="C5" t="n">
-        <v>141.4207567967531</v>
+        <v>196.61952146803</v>
       </c>
       <c r="D5" t="n">
-        <v>204.1544350981243</v>
+        <v>119.9941131515664</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.69192081397831</v>
+        <v>59.53219903782235</v>
       </c>
       <c r="C6" t="n">
-        <v>284.2169421271559</v>
+        <v>345.8422272704325</v>
       </c>
       <c r="D6" t="n">
-        <v>118.9033914521482</v>
+        <v>79.21525876026665</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.87668500435917</v>
+        <v>30.60205768907732</v>
       </c>
       <c r="C7" t="n">
-        <v>355.0677104472396</v>
+        <v>378.4234883312713</v>
       </c>
       <c r="D7" t="n">
-        <v>56.23352675155305</v>
+        <v>47.9691745772034</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.425538724295373</v>
+        <v>8.92899537012474</v>
       </c>
       <c r="C8" t="n">
-        <v>288.8988969287089</v>
+        <v>267.1188241099934</v>
       </c>
       <c r="D8" t="n">
-        <v>36.71736413883071</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>139.0046756966016</v>
+        <v>132.0156137900686</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>48.82722207071512</v>
+        <v>52.24370408149402</v>
       </c>
       <c r="D10" t="n">
-        <v>26.05067533218912</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>25.05518316008284</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>17.17076734727672</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>12.29148125717007</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.370740779306799</v>
+        <v>5.51251335934584</v>
       </c>
       <c r="C2" t="n">
-        <v>12.24239387195773</v>
+        <v>7.929576207201487</v>
       </c>
       <c r="D2" t="n">
-        <v>15.28581175512284</v>
+        <v>7.352308557104362</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.304742698944011</v>
+        <v>2.449460522095792</v>
       </c>
       <c r="C2" t="n">
-        <v>6.123160431387356</v>
+        <v>3.756166716448297</v>
       </c>
       <c r="D2" t="n">
-        <v>7.38077924052752</v>
+        <v>8.2486442110817</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.25926350937917</v>
+        <v>15.10909716835841</v>
       </c>
       <c r="C3" t="n">
-        <v>23.92028281397354</v>
+        <v>20.14546289114455</v>
       </c>
       <c r="D3" t="n">
-        <v>80.95491569219199</v>
+        <v>53.08800710714627</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.10198825471721</v>
+        <v>44.63123238276425</v>
       </c>
       <c r="C4" t="n">
-        <v>73.75575977695013</v>
+        <v>102.0379476408922</v>
       </c>
       <c r="D4" t="n">
-        <v>196.0864324646239</v>
+        <v>116.4215332558123</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.12078032981814</v>
+        <v>34.5820628820939</v>
       </c>
       <c r="C5" t="n">
-        <v>228.5263218560513</v>
+        <v>293.8616315736766</v>
       </c>
       <c r="D5" t="n">
-        <v>183.218665305061</v>
+        <v>110.0539176460675</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.16858286768997</v>
+        <v>18.99878157258428</v>
       </c>
       <c r="C6" t="n">
-        <v>286.7930481030995</v>
+        <v>313.640902571137</v>
       </c>
       <c r="D6" t="n">
-        <v>89.31842438467058</v>
+        <v>66.29447722467438</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.251949307092936</v>
+        <v>5.868887775987432</v>
       </c>
       <c r="C7" t="n">
-        <v>203.135380981116</v>
+        <v>187.8044088315978</v>
       </c>
       <c r="D7" t="n">
-        <v>32.93763547748049</v>
+        <v>31.85967649821749</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>102.3913768144211</v>
+        <v>97.30101496790137</v>
       </c>
       <c r="D8" t="n">
-        <v>23.86628669023996</v>
+        <v>24.61732368398877</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>37.27499683484289</v>
+        <v>39.82655911818034</v>
       </c>
       <c r="D9" t="n">
-        <v>19.85781081380023</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.4988920646734</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>18.79065105928395</v>
+        <v>19.64477156197868</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.74879576089983</v>
+        <v>16.52575910558656</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.70345544005523</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>10.14636252339079</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.844344083381262</v>
+        <v>6.282203559475339</v>
       </c>
       <c r="C2" t="n">
-        <v>8.2486442110817</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="D2" t="n">
-        <v>25.47537117750048</v>
+        <v>9.468956607460486</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.29224202069606</v>
+        <v>11.71225011166445</v>
       </c>
       <c r="C3" t="n">
-        <v>30.84651286743478</v>
+        <v>19.97856578142259</v>
       </c>
       <c r="D3" t="n">
-        <v>15.97794388661684</v>
+        <v>9.311876974780997</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3965285559105</v>
+        <v>13.39843226314587</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13476714564911</v>
+        <v>70.14473361294012</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576062183048294</v>
+        <v>1.576286148605396</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.769911184307752</v>
+        <v>4.156719779780995</v>
       </c>
       <c r="C2" t="n">
-        <v>4.663301595172349</v>
+        <v>3.272165098254619</v>
       </c>
       <c r="D2" t="n">
-        <v>33.91054745238908</v>
+        <v>10.15618000043325</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.80122929985241</v>
+        <v>17.70091110756999</v>
       </c>
       <c r="C3" t="n">
-        <v>31.6711809390021</v>
+        <v>18.25559856046944</v>
       </c>
       <c r="D3" t="n">
-        <v>33.51686662298611</v>
+        <v>15.01583113645496</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.92488845285851</v>
+        <v>13.65611056607313</v>
       </c>
       <c r="C4" t="n">
-        <v>47.54113257815179</v>
+        <v>31.47286790274425</v>
       </c>
       <c r="D4" t="n">
-        <v>23.44511692511808</v>
+        <v>19.94813160259094</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.117048960983624</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
-        <v>39.82655911818034</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4980,10 +4980,10 @@
         <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
-        <v>26.53664044579129</v>
+        <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43446986836818</v>
+        <v>15.44305939473562</v>
       </c>
       <c r="C21" t="n">
-        <v>86.10809505510667</v>
+        <v>86.15601557063033</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249362077551195</v>
+        <v>3.25117039889171</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.474806035956962</v>
+        <v>4.141993564217293</v>
       </c>
       <c r="C2" t="n">
-        <v>9.040914608408876</v>
+        <v>5.821763886183585</v>
       </c>
       <c r="D2" t="n">
-        <v>38.98029259711961</v>
+        <v>9.013425672689966</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.23534171157875</v>
+        <v>15.83559046950105</v>
       </c>
       <c r="C3" t="n">
-        <v>23.58648859452962</v>
+        <v>14.90293015046658</v>
       </c>
       <c r="D3" t="n">
-        <v>52.86711387369073</v>
+        <v>19.65458903902115</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.72214970416493</v>
+        <v>25.25742318715769</v>
       </c>
       <c r="C4" t="n">
-        <v>65.91944960165209</v>
+        <v>39.56443248114646</v>
       </c>
       <c r="D4" t="n">
-        <v>34.95709050511617</v>
+        <v>22.99842171968578</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.989282890711298</v>
+        <v>12.24730261047896</v>
       </c>
       <c r="C5" t="n">
-        <v>51.56629816556373</v>
+        <v>35.95650966803944</v>
       </c>
       <c r="D5" t="n">
-        <v>31.3668391506856</v>
+        <v>29.62423697564751</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>40.93593402397924</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.04418831335365</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5305,10 +5305,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.71806670766131</v>
+        <v>16.74086859470061</v>
       </c>
       <c r="C21" t="n">
-        <v>101.1443035813509</v>
+        <v>102.1192984276737</v>
       </c>
       <c r="D21" t="n">
-        <v>4.179516676915327</v>
+        <v>5.022260578410183</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.266094685579891</v>
+        <v>4.432590884674349</v>
       </c>
       <c r="C2" t="n">
-        <v>11.50510134606837</v>
+        <v>8.418486563916399</v>
       </c>
       <c r="D2" t="n">
-        <v>29.73517446622739</v>
+        <v>24.55841882173396</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.72130682518092</v>
+        <v>14.93729132011522</v>
       </c>
       <c r="C3" t="n">
-        <v>30.3016428915778</v>
+        <v>19.42387832852314</v>
       </c>
       <c r="D3" t="n">
-        <v>69.67954330891737</v>
+        <v>22.13350199224434</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.54271085846601</v>
+        <v>28.10350978176919</v>
       </c>
       <c r="C4" t="n">
-        <v>61.52907386826035</v>
+        <v>38.2881604656256</v>
       </c>
       <c r="D4" t="n">
-        <v>51.26784686347268</v>
+        <v>27.19735665074939</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.91122610045706</v>
+        <v>25.35363446217388</v>
       </c>
       <c r="C5" t="n">
-        <v>88.74999246391167</v>
+        <v>56.3768619163731</v>
       </c>
       <c r="D5" t="n">
-        <v>36.59464567579986</v>
+        <v>31.3668391506856</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.700649065662736</v>
+        <v>11.27046364475338</v>
       </c>
       <c r="C6" t="n">
-        <v>47.41645061971246</v>
+        <v>35.70321876034376</v>
       </c>
       <c r="D6" t="n">
-        <v>37.75605320992383</v>
+        <v>37.79630486579796</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.25974653546468</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.61405964570653</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>42.04530892977813</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>48.9695754878309</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.28806265463436</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.51560713784138</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
         <v>45.7857676829585</v>
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.77765165941727</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.02723241353186</v>
+        <v>18.07520763750187</v>
       </c>
       <c r="C21" t="n">
-        <v>116.7477908685873</v>
+        <v>117.9192117303693</v>
       </c>
       <c r="D21" t="n">
-        <v>6.009077471177287</v>
+        <v>6.885793385714996</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.633268326968198</v>
+        <v>5.461462478725005</v>
       </c>
       <c r="C2" t="n">
-        <v>10.59109423341459</v>
+        <v>11.03288070032565</v>
       </c>
       <c r="D2" t="n">
-        <v>28.45301196448106</v>
+        <v>20.3457394228109</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.66240196292611</v>
+        <v>13.48430471782994</v>
       </c>
       <c r="C3" t="n">
-        <v>35.82397372796611</v>
+        <v>25.56471021858694</v>
       </c>
       <c r="D3" t="n">
-        <v>71.68230862558086</v>
+        <v>33.74266859496287</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.36104647545135</v>
+        <v>20.91809833438679</v>
       </c>
       <c r="C4" t="n">
-        <v>57.30461349688632</v>
+        <v>37.01188845010475</v>
       </c>
       <c r="D4" t="n">
-        <v>62.47351515974578</v>
+        <v>27.58023825540564</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.42602175038089</v>
+        <v>20.73942025221387</v>
       </c>
       <c r="C5" t="n">
-        <v>75.59457322700442</v>
+        <v>47.39387042251478</v>
       </c>
       <c r="D5" t="n">
-        <v>37.40458753180348</v>
+        <v>27.7343726449724</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.18366893615217</v>
+        <v>12.5585166327252</v>
       </c>
       <c r="C6" t="n">
-        <v>63.59761628110839</v>
+        <v>43.71329827929349</v>
       </c>
       <c r="D6" t="n">
-        <v>31.15478164656829</v>
+        <v>30.22899356146354</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>5.629341336151211</v>
       </c>
       <c r="C7" t="n">
-        <v>28.62579956042849</v>
+        <v>23.71509754378595</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>31.38058361854505</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>29.45733986592554</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.52187317249857</v>
+        <v>22.18749811597791</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>30.17892442854696</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.038501022153874</v>
+        <v>7.0678871310458</v>
       </c>
       <c r="C21" t="n">
-        <v>65.98594708269256</v>
+        <v>67.14492774493509</v>
       </c>
       <c r="D21" t="n">
-        <v>4.399063138846171</v>
+        <v>5.30091534828435</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.263730279543897</v>
+        <v>5.178719139901924</v>
       </c>
       <c r="C2" t="n">
-        <v>5.378995671568275</v>
+        <v>8.714974370598936</v>
       </c>
       <c r="D2" t="n">
-        <v>38.86837335883547</v>
+        <v>19.47198396603124</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.61255381418778</v>
+        <v>17.07750131537327</v>
       </c>
       <c r="C3" t="n">
-        <v>39.25027321578748</v>
+        <v>37.27205159173015</v>
       </c>
       <c r="D3" t="n">
-        <v>78.26001824403448</v>
+        <v>43.16744655573225</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.9766433437431</v>
+        <v>24.68310078017331</v>
       </c>
       <c r="C4" t="n">
-        <v>77.08682973745954</v>
+        <v>54.61167954413732</v>
       </c>
       <c r="D4" t="n">
-        <v>85.54851320036282</v>
+        <v>39.43680527959437</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.90555659840983</v>
+        <v>27.19441140763665</v>
       </c>
       <c r="C5" t="n">
-        <v>93.60964359993338</v>
+        <v>60.77018289287758</v>
       </c>
       <c r="D5" t="n">
-        <v>52.13080309550564</v>
+        <v>31.71045084717198</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.75098024048658</v>
+        <v>21.93715245139498</v>
       </c>
       <c r="C6" t="n">
-        <v>95.2354177981661</v>
+        <v>63.07434475474484</v>
       </c>
       <c r="D6" t="n">
-        <v>35.90447703971436</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.982991493858314</v>
+        <v>11.19879606234337</v>
       </c>
       <c r="C7" t="n">
-        <v>64.79731197569798</v>
+        <v>47.54996830749001</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>33.71616140694821</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>26.62008900065226</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.20008090968388</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
         <v>34.82848155585983</v>
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.41280136633594</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>10.08745766113597</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.251449203144393</v>
+        <v>7.295948745844007</v>
       </c>
       <c r="C21" t="n">
-        <v>75.23378548262309</v>
+        <v>77.51945542459258</v>
       </c>
       <c r="D21" t="n">
-        <v>5.438586902358295</v>
+        <v>6.383955152613506</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.372704274715294</v>
+        <v>4.228387362191013</v>
       </c>
       <c r="C2" t="n">
-        <v>5.14337622254904</v>
+        <v>6.601271563355553</v>
       </c>
       <c r="D2" t="n">
-        <v>35.4420738710141</v>
+        <v>24.20989838672634</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.96812640957437</v>
+        <v>17.63218876827272</v>
       </c>
       <c r="C3" t="n">
-        <v>28.62776305583699</v>
+        <v>35.22510762837555</v>
       </c>
       <c r="D3" t="n">
-        <v>90.39441986852506</v>
+        <v>48.72904730029043</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.03068052520568</v>
+        <v>29.63503620039422</v>
       </c>
       <c r="C4" t="n">
-        <v>88.89234588102745</v>
+        <v>77.30379598009809</v>
       </c>
       <c r="D4" t="n">
-        <v>104.4501017502267</v>
+        <v>51.82940655030185</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.77779052813751</v>
+        <v>33.13398501832986</v>
       </c>
       <c r="C5" t="n">
-        <v>119.0859965251381</v>
+        <v>84.55302102825655</v>
       </c>
       <c r="D5" t="n">
-        <v>69.45865007546185</v>
+        <v>39.19627709205391</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.43904651244335</v>
+        <v>30.30949687321178</v>
       </c>
       <c r="C6" t="n">
-        <v>123.8140934687908</v>
+        <v>82.31463626257383</v>
       </c>
       <c r="D6" t="n">
-        <v>43.9548082145382</v>
+        <v>35.54221213684728</v>
       </c>
     </row>
     <row r="7">
@@ -6448,10 +6448,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.09142570968197</v>
+        <v>19.64280806657018</v>
       </c>
       <c r="C7" t="n">
-        <v>103.1846289594525</v>
+        <v>72.46279805045707</v>
       </c>
       <c r="D7" t="n">
         <v>36.17151241526948</v>
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.760715602071035</v>
+        <v>9.346238144429634</v>
       </c>
       <c r="C8" t="n">
-        <v>58.4974369575462</v>
+        <v>47.14843349645307</v>
       </c>
       <c r="D8" t="n">
-        <v>33.54631905411351</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>30.84062238120929</v>
+        <v>29.06562253193106</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>25.58827216348886</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
         <v>35.53926689373453</v>
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
         <v>31.73990327829938</v>
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>10.08745766113597</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.448822931783596</v>
+        <v>7.512033913525388</v>
       </c>
       <c r="C21" t="n">
-        <v>83.79925798256545</v>
+        <v>87.32739424473263</v>
       </c>
       <c r="D21" t="n">
-        <v>6.517720065310646</v>
+        <v>7.512033913525388</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_38_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_38_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497631695651</v>
+        <v>10.84497655837041</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907188874143</v>
+        <v>37.78907272994263</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.979424355939822</v>
+        <v>1.116247139728623</v>
       </c>
       <c r="C2" t="n">
-        <v>9.291260272991813</v>
+        <v>4.026147335116169</v>
       </c>
       <c r="D2" t="n">
-        <v>18.57957530287089</v>
+        <v>19.54856028696249</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.06139244147782</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C3" t="n">
-        <v>29.66350688381738</v>
+        <v>48.10563750809371</v>
       </c>
       <c r="D3" t="n">
-        <v>56.28850462299088</v>
+        <v>78.24529202847079</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.84298678724529</v>
+        <v>20.54797944988574</v>
       </c>
       <c r="C4" t="n">
-        <v>83.36608805382215</v>
+        <v>123.747334624902</v>
       </c>
       <c r="D4" t="n">
-        <v>63.90293981712914</v>
+        <v>78.0567964692554</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.97538385859838</v>
+        <v>20.0521968592411</v>
       </c>
       <c r="C5" t="n">
-        <v>116.0180349493668</v>
+        <v>127.2099587777805</v>
       </c>
       <c r="D5" t="n">
-        <v>48.05655012288138</v>
+        <v>45.03767593232243</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.31957639216151</v>
+        <v>13.12203981496287</v>
       </c>
       <c r="C6" t="n">
-        <v>108.719722515996</v>
+        <v>89.72094094341176</v>
       </c>
       <c r="D6" t="n">
-        <v>40.01014593887452</v>
+        <v>29.58496706747763</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.20659329071511</v>
+        <v>6.168320825782709</v>
       </c>
       <c r="C7" t="n">
-        <v>97.37562779342413</v>
+        <v>47.25053525769474</v>
       </c>
       <c r="D7" t="n">
-        <v>38.20765715387736</v>
+        <v>29.10489244010094</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.60487975900305</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>72.43334561932966</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>36.55046702910875</v>
+        <v>30.70906818884022</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>44.81874619427537</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
-        <v>34.50155957034565</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.274128593663113</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>37.29659528433633</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>37.31623023842126</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>37.5351599764683</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.85539932116455</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.713771790186439</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>96.42214737733049</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.677993263959744</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.42692138262712</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C2" t="n">
-        <v>10.48212023824319</v>
+        <v>6.71613604475243</v>
       </c>
       <c r="D2" t="n">
-        <v>16.59939018340507</v>
+        <v>18.41464168855742</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.3608254912731</v>
+        <v>7.17166697952295</v>
       </c>
       <c r="C3" t="n">
-        <v>32.90327430783185</v>
+        <v>29.7960428238907</v>
       </c>
       <c r="D3" t="n">
-        <v>57.48132808365075</v>
+        <v>75.6976567359503</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.29418982057133</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="C4" t="n">
-        <v>77.77601662584082</v>
+        <v>121.8712147620863</v>
       </c>
       <c r="D4" t="n">
-        <v>74.78954010952202</v>
+        <v>98.54096231836509</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.97600575340413</v>
+        <v>25.42726553999239</v>
       </c>
       <c r="C5" t="n">
-        <v>134.8675908709056</v>
+        <v>182.1387428303895</v>
       </c>
       <c r="D5" t="n">
-        <v>58.80668748438396</v>
+        <v>61.80101798233672</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.2026095466359</v>
+        <v>19.72331137831842</v>
       </c>
       <c r="C6" t="n">
-        <v>144.141179685221</v>
+        <v>146.7172856611646</v>
       </c>
       <c r="D6" t="n">
-        <v>45.04160292313942</v>
+        <v>36.66925850132262</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.9500383447372</v>
+        <v>10.24061030299848</v>
       </c>
       <c r="C7" t="n">
-        <v>126.9596131131975</v>
+        <v>87.37456393026187</v>
       </c>
       <c r="D7" t="n">
-        <v>41.14210104187108</v>
+        <v>30.96137734883166</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.61455836732527</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>99.5541259491478</v>
+        <v>45.64635950895544</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>31.71045084717197</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.53749902030851</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>66.89530681967339</v>
+        <v>34.72343455150543</v>
       </c>
       <c r="D9" t="n">
-        <v>36.16562192904399</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>41.99425804915732</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>37.72365553568369</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>38.20471191076462</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>28.87810872041993</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>51.90009238500763</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>45.13585070274711</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.900481876489169</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>105.6689450980426</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.875602345611462</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.896597695884596</v>
+        <v>0.6587527095496097</v>
       </c>
       <c r="C2" t="n">
-        <v>15.59702577736908</v>
+        <v>2.935425635697963</v>
       </c>
       <c r="D2" t="n">
-        <v>21.19004244846316</v>
+        <v>12.57029760517616</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.08655802888974</v>
+        <v>6.612070788102269</v>
       </c>
       <c r="C3" t="n">
-        <v>36.44738352016284</v>
+        <v>29.80586030093317</v>
       </c>
       <c r="D3" t="n">
-        <v>56.97572801596364</v>
+        <v>75.72220042855649</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.6560538128109</v>
+        <v>22.70487915611599</v>
       </c>
       <c r="C4" t="n">
-        <v>79.66489920881168</v>
+        <v>115.5791937255685</v>
       </c>
       <c r="D4" t="n">
-        <v>83.97869862127216</v>
+        <v>110.652783745658</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.49771469498668</v>
+        <v>25.37817815478006</v>
       </c>
       <c r="C5" t="n">
-        <v>137.1010668980671</v>
+        <v>219.3469808213437</v>
       </c>
       <c r="D5" t="n">
-        <v>68.6732519120644</v>
+        <v>70.61220362795184</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.24035792775378</v>
+        <v>14.89311267342412</v>
       </c>
       <c r="C6" t="n">
-        <v>173.9274050320692</v>
+        <v>183.3865441624872</v>
       </c>
       <c r="D6" t="n">
-        <v>51.84413276586557</v>
+        <v>37.23278168356029</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>44.25620475974196</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>163.7299916280575</v>
+        <v>81.92488242398782</v>
       </c>
       <c r="D7" t="n">
-        <v>43.83699849002857</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.12492830481337</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>129.5956056991002</v>
+        <v>40.80634332701867</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.30781111524376</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>92.52186714362787</v>
+        <v>25.95937279569415</v>
       </c>
       <c r="D9" t="n">
-        <v>37.71874679716245</v>
+        <v>39.82655911818034</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.541205026947251</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>57.79548734900973</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>40.15937158992001</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
-        <v>37.31623023842126</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>31.21957699504857</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>28.5776939229204</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>44.860961345558</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>39.05883241345935</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.07135184433297</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>114.0078448012032</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.09810878595783</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.981608835526568</v>
+        <v>0.7795076771719675</v>
       </c>
       <c r="C2" t="n">
-        <v>10.48113849053895</v>
+        <v>6.590472338608838</v>
       </c>
       <c r="D2" t="n">
-        <v>17.38871533761951</v>
+        <v>12.96692367769187</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.87963024747192</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C3" t="n">
-        <v>57.02972413969722</v>
+        <v>19.78712497909446</v>
       </c>
       <c r="D3" t="n">
-        <v>62.12008598621694</v>
+        <v>68.65852569650069</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.3775562599743</v>
+        <v>18.13582534055133</v>
       </c>
       <c r="C4" t="n">
-        <v>113.5626839410455</v>
+        <v>94.90358707413067</v>
       </c>
       <c r="D4" t="n">
-        <v>79.95844177238148</v>
+        <v>123.2495885388488</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.86338250485623</v>
+        <v>29.59969328304134</v>
       </c>
       <c r="C5" t="n">
-        <v>103.9179944945249</v>
+        <v>218.2916020392783</v>
       </c>
       <c r="D5" t="n">
-        <v>50.09367660919352</v>
+        <v>90.2962450981004</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.45162930614931</v>
+        <v>22.82268888062561</v>
       </c>
       <c r="C6" t="n">
-        <v>107.8341860867654</v>
+        <v>264.7351406840822</v>
       </c>
       <c r="D6" t="n">
-        <v>28.86043726174349</v>
+        <v>48.02022545782425</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.94224111636546</v>
+        <v>8.982991493858314</v>
       </c>
       <c r="C7" t="n">
-        <v>91.0875337477233</v>
+        <v>163.9096514579347</v>
       </c>
       <c r="D7" t="n">
-        <v>28.14670668075605</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.26555490623215</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>68.17746932141974</v>
+        <v>69.59609475405638</v>
       </c>
       <c r="D8" t="n">
-        <v>27.78836876870596</v>
+        <v>37.1346069131356</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>44.04218376021615</v>
+        <v>36.38749691020377</v>
       </c>
       <c r="D9" t="n">
-        <v>27.5124976638126</v>
+        <v>40.60312155223957</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
-        <v>29.18245050873644</v>
+        <v>31.74481201682062</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>23.29196428325557</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>38.02505208088746</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>47.22206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.688827035482766</v>
+        <v>0.4614214209960009</v>
       </c>
       <c r="C2" t="n">
-        <v>5.043237956715865</v>
+        <v>3.876921684070654</v>
       </c>
       <c r="D2" t="n">
-        <v>12.19036124363264</v>
+        <v>8.995754214013523</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.75615102091507</v>
+        <v>3.706097583531709</v>
       </c>
       <c r="C3" t="n">
-        <v>49.72061248157971</v>
+        <v>22.90908267859932</v>
       </c>
       <c r="D3" t="n">
-        <v>61.9139189683251</v>
+        <v>64.32410958225101</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.20485077948487</v>
+        <v>14.81751810019711</v>
       </c>
       <c r="C4" t="n">
-        <v>130.7923561505771</v>
+        <v>76.46145644985432</v>
       </c>
       <c r="D4" t="n">
-        <v>91.58527983377644</v>
+        <v>128.6354564443468</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.0295188510522</v>
+        <v>30.65507206510666</v>
       </c>
       <c r="C5" t="n">
-        <v>155.0915935783899</v>
+        <v>208.0323385298992</v>
       </c>
       <c r="D5" t="n">
-        <v>62.46369768270332</v>
+        <v>107.5750046928443</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.8453511932813</v>
+        <v>27.49188096202344</v>
       </c>
       <c r="C6" t="n">
-        <v>136.6141200367607</v>
+        <v>307.0798826636557</v>
       </c>
       <c r="D6" t="n">
-        <v>34.45541742824607</v>
+        <v>58.44540432922113</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.86428213710246</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>117.1980956898715</v>
+        <v>239.7859862760579</v>
       </c>
       <c r="D7" t="n">
-        <v>30.60205768907732</v>
+        <v>38.98618308334508</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>88.78926237208152</v>
+        <v>104.2272450213626</v>
       </c>
       <c r="D8" t="n">
-        <v>28.95664853675967</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>50.14374574211007</v>
+        <v>45.70624611891449</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>34.02246669067321</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>33.02599277086271</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>30.38607319414302</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.109015052900402</v>
+        <v>0.7834346679889547</v>
       </c>
       <c r="C2" t="n">
-        <v>7.133378819057324</v>
+        <v>8.371362674112552</v>
       </c>
       <c r="D2" t="n">
-        <v>15.09044396197772</v>
+        <v>14.38064037180728</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.78850763742621</v>
+        <v>2.660536278508856</v>
       </c>
       <c r="C3" t="n">
-        <v>33.60031517784709</v>
+        <v>19.09499284760046</v>
       </c>
       <c r="D3" t="n">
-        <v>58.10964661436871</v>
+        <v>57.62368150076654</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.17704304859647</v>
+        <v>11.26948189704914</v>
       </c>
       <c r="C4" t="n">
-        <v>127.3081335482051</v>
+        <v>67.23400977763856</v>
       </c>
       <c r="D4" t="n">
-        <v>99.24291192690157</v>
+        <v>130.6519662288698</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.8772090881737</v>
+        <v>27.70982895236623</v>
       </c>
       <c r="C5" t="n">
-        <v>199.6383956585889</v>
+        <v>177.3527227721863</v>
       </c>
       <c r="D5" t="n">
-        <v>79.10432126968676</v>
+        <v>124.4119778206771</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.79630486579796</v>
+        <v>33.08686112852601</v>
       </c>
       <c r="C6" t="n">
-        <v>188.377749490878</v>
+        <v>318.350346308409</v>
       </c>
       <c r="D6" t="n">
-        <v>44.39757642915352</v>
+        <v>73.53977528201584</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.24840753137022</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="C7" t="n">
-        <v>156.2441653831756</v>
+        <v>329.2565815548868</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>44.67541102945535</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.68556299720053</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>120.2493675546706</v>
+        <v>190.7633964121977</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>40.63944621729671</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.545311944213482</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>76.54686850012379</v>
+        <v>77.87811838708245</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>45.26838664282043</v>
+        <v>40.57072387799944</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>34.65078522139116</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>26.68684784454105</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>26.79680358741669</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>19.97365704290136</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>33.68376373270807</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>39.67831521483909</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.00709321810798</v>
+        <v>0.5448699758569798</v>
       </c>
       <c r="C2" t="n">
-        <v>3.329106465100934</v>
+        <v>4.553345852296707</v>
       </c>
       <c r="D2" t="n">
-        <v>10.52335364182156</v>
+        <v>10.46837577038374</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.15666302651876</v>
+        <v>3.966260725157114</v>
       </c>
       <c r="C3" t="n">
-        <v>32.94745295452295</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D3" t="n">
-        <v>58.61033794353458</v>
+        <v>63.38654052469531</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.4015034199705</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="C4" t="n">
-        <v>124.6790131962322</v>
+        <v>97.77519910905259</v>
       </c>
       <c r="D4" t="n">
-        <v>105.8540009672996</v>
+        <v>132.7961032149448</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.64435495581795</v>
+        <v>19.90493470360408</v>
       </c>
       <c r="C5" t="n">
-        <v>237.4847696573035</v>
+        <v>267.5507930998621</v>
       </c>
       <c r="D5" t="n">
-        <v>83.57127332400975</v>
+        <v>112.287393673229</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.28182801104362</v>
+        <v>10.94845039776043</v>
       </c>
       <c r="C6" t="n">
-        <v>227.1400940976548</v>
+        <v>285.5049951151277</v>
       </c>
       <c r="D6" t="n">
-        <v>44.23656980565704</v>
+        <v>62.02780170201773</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.042878103817369</v>
+        <v>4.07228947721577</v>
       </c>
       <c r="C7" t="n">
-        <v>161.5740736695315</v>
+        <v>134.1460063082842</v>
       </c>
       <c r="D7" t="n">
-        <v>34.07548106670254</v>
+        <v>34.6743471662931</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.506221962492859</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C8" t="n">
-        <v>94.12996988318417</v>
+        <v>57.32915718949249</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79389940203295</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>34.50155957034565</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>26.5140602485936</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>24.05772749256809</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>21.32356013624072</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>33.68376373270807</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.377212102609028</v>
+        <v>0.2856885819358218</v>
       </c>
       <c r="C2" t="n">
-        <v>3.311435006424491</v>
+        <v>2.149045724596268</v>
       </c>
       <c r="D2" t="n">
-        <v>13.33017032826319</v>
+        <v>8.284968876138832</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.92394776288327</v>
+        <v>2.920699420134261</v>
       </c>
       <c r="C3" t="n">
-        <v>22.78636421556847</v>
+        <v>22.09423208407447</v>
       </c>
       <c r="D3" t="n">
-        <v>53.85377031645879</v>
+        <v>57.43224069843841</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.48709539668921</v>
+        <v>12.60956751334603</v>
       </c>
       <c r="C4" t="n">
-        <v>103.7226267013798</v>
+        <v>78.50349167468769</v>
       </c>
       <c r="D4" t="n">
-        <v>111.2398688727976</v>
+        <v>128.3802020412427</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.71356032120075</v>
+        <v>18.80046853632642</v>
       </c>
       <c r="C5" t="n">
-        <v>235.8403422526901</v>
+        <v>205.3570760358266</v>
       </c>
       <c r="D5" t="n">
-        <v>98.29748888771192</v>
+        <v>117.490656505737</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.45920555034281</v>
+        <v>10.90819874188631</v>
       </c>
       <c r="C6" t="n">
-        <v>295.8094190189022</v>
+        <v>284.7402136535194</v>
       </c>
       <c r="D6" t="n">
-        <v>56.11080828852221</v>
+        <v>66.49573550404497</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.44507586738907</v>
+        <v>3.413536767666159</v>
       </c>
       <c r="C7" t="n">
-        <v>235.534036968965</v>
+        <v>180.1988093667978</v>
       </c>
       <c r="D7" t="n">
-        <v>38.08788393395925</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>143.3646172511617</v>
+        <v>67.42643232767094</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>26.20284622634736</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>64.78749449865549</v>
+        <v>28.51093507903161</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>20.74531073843935</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>16.79770321966293</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>19.64477156197868</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.6997904911455</v>
+        <v>12.9718324162131</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>17.23654444346124</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.428843820306609</v>
+        <v>0.4751658888554562</v>
       </c>
       <c r="C2" t="n">
-        <v>2.752820562708056</v>
+        <v>4.824308218668826</v>
       </c>
       <c r="D2" t="n">
-        <v>10.34369381194439</v>
+        <v>8.557894737919446</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.22061549601505</v>
+        <v>1.880046853632642</v>
       </c>
       <c r="C3" t="n">
-        <v>18.64338890364693</v>
+        <v>14.1420756796753</v>
       </c>
       <c r="D3" t="n">
-        <v>52.45968857642831</v>
+        <v>50.95270585040946</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.81143199198916</v>
+        <v>9.099819470663686</v>
       </c>
       <c r="C4" t="n">
-        <v>86.60781897324512</v>
+        <v>65.54933071715104</v>
       </c>
       <c r="D4" t="n">
-        <v>113.8562265046153</v>
+        <v>128.2908630001562</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.8677357684965</v>
+        <v>19.29134238844983</v>
       </c>
       <c r="C5" t="n">
-        <v>224.7956805799135</v>
+        <v>174.849266126357</v>
       </c>
       <c r="D5" t="n">
-        <v>108.4585776266664</v>
+        <v>136.2665813494573</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.3887817575443</v>
+        <v>17.63022527286423</v>
       </c>
       <c r="C6" t="n">
-        <v>336.222081516518</v>
+        <v>307.200637631278</v>
       </c>
       <c r="D6" t="n">
-        <v>66.1334706011779</v>
+        <v>86.17879522648927</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.76825078853552</v>
+        <v>7.72537268471815</v>
       </c>
       <c r="C7" t="n">
-        <v>301.7087409737213</v>
+        <v>298.7742970857275</v>
       </c>
       <c r="D7" t="n">
-        <v>41.74096714146164</v>
+        <v>43.41779222031519</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>187.2585571080366</v>
+        <v>150.7915386337888</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>28.87319998189869</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>75.10468112258522</v>
+        <v>54.47030787472577</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>22.40937309713768</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>20.4988920646734</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>12.80100831567416</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.386047831947249</v>
+        <v>0.776562434059227</v>
       </c>
       <c r="C2" t="n">
-        <v>6.522731747015809</v>
+        <v>6.637596228412685</v>
       </c>
       <c r="D2" t="n">
-        <v>11.08785857176348</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.25082869066845</v>
+        <v>1.722967220953152</v>
       </c>
       <c r="C3" t="n">
-        <v>14.86366024229671</v>
+        <v>16.49336143134641</v>
       </c>
       <c r="D3" t="n">
-        <v>49.00884539600077</v>
+        <v>46.4170314567892</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.48937768726719</v>
+        <v>6.394122797759476</v>
       </c>
       <c r="C4" t="n">
-        <v>68.68895987533233</v>
+        <v>50.0936766091935</v>
       </c>
       <c r="D4" t="n">
-        <v>113.6392602619768</v>
+        <v>123.8366736659884</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.23589115758906</v>
+        <v>16.8369731278328</v>
       </c>
       <c r="C5" t="n">
-        <v>196.61952146803</v>
+        <v>148.2439033412684</v>
       </c>
       <c r="D5" t="n">
-        <v>119.9941131515664</v>
+        <v>150.1337676719435</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.53219903782235</v>
+        <v>21.65539086027615</v>
       </c>
       <c r="C6" t="n">
-        <v>345.8422272704325</v>
+        <v>294.9238825896716</v>
       </c>
       <c r="D6" t="n">
-        <v>79.21525876026665</v>
+        <v>106.1033648841783</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.60205768907732</v>
+        <v>13.59426046070558</v>
       </c>
       <c r="C7" t="n">
-        <v>378.4234883312713</v>
+        <v>365.4879805801153</v>
       </c>
       <c r="D7" t="n">
-        <v>47.9691745772034</v>
+        <v>54.97590794241288</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>267.1188241099934</v>
+        <v>265.1995073481909</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>33.21252483466959</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>132.0156137900686</v>
+        <v>114.487490278446</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>24.29531043699581</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>52.24370408149402</v>
+        <v>42.27896488338889</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>21.06830573313655</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>21.32356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>25.05518316008284</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>17.17076734727672</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>7.883434065101886</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.51251335934584</v>
+        <v>5.294565369003049</v>
       </c>
       <c r="C2" t="n">
-        <v>7.929576207201487</v>
+        <v>12.21686843164731</v>
       </c>
       <c r="D2" t="n">
-        <v>7.352308557104362</v>
+        <v>4.11548637620263</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.449460522095792</v>
+        <v>1.183987731321653</v>
       </c>
       <c r="C2" t="n">
-        <v>3.756166716448297</v>
+        <v>9.875400157018666</v>
       </c>
       <c r="D2" t="n">
-        <v>8.2486442110817</v>
+        <v>15.75017841923158</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.10909716835841</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C3" t="n">
-        <v>20.14546289114455</v>
+        <v>20.75905520629881</v>
       </c>
       <c r="D3" t="n">
-        <v>53.08800710714627</v>
+        <v>48.43452298901639</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.63123238276425</v>
+        <v>4.87535909928966</v>
       </c>
       <c r="C4" t="n">
-        <v>102.0379476408922</v>
+        <v>45.85645351766426</v>
       </c>
       <c r="D4" t="n">
-        <v>116.4215332558123</v>
+        <v>119.586687854304</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.5820628820939</v>
+        <v>13.96536109291088</v>
       </c>
       <c r="C5" t="n">
-        <v>293.8616315736766</v>
+        <v>121.810346404423</v>
       </c>
       <c r="D5" t="n">
-        <v>110.0539176460675</v>
+        <v>158.2331862319797</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.99878157258428</v>
+        <v>22.09815907489146</v>
       </c>
       <c r="C6" t="n">
-        <v>313.640902571137</v>
+        <v>270.8533923769483</v>
       </c>
       <c r="D6" t="n">
-        <v>66.29447722467438</v>
+        <v>122.4857888249448</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.868887775987432</v>
+        <v>18.62473569726624</v>
       </c>
       <c r="C7" t="n">
-        <v>187.8044088315978</v>
+        <v>391.1793362525501</v>
       </c>
       <c r="D7" t="n">
-        <v>31.85967649821749</v>
+        <v>68.51028179315941</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="C8" t="n">
-        <v>97.30101496790137</v>
+        <v>360.7481026640117</v>
       </c>
       <c r="D8" t="n">
-        <v>24.61732368398877</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>39.82655911818034</v>
+        <v>203.0156077611979</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>26.5140602485936</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>22.776546738526</v>
+        <v>78.72143966503049</v>
       </c>
       <c r="D10" t="n">
-        <v>19.64477156197868</v>
+        <v>21.78007281871549</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.52575910558656</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>16.70345544005523</v>
+        <v>19.19120412261664</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>13.88583952886689</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.14636252339079</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>10.75013736150257</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.282203559475339</v>
+        <v>5.833544858634546</v>
       </c>
       <c r="C2" t="n">
-        <v>4.422773407631881</v>
+        <v>10.53611636197677</v>
       </c>
       <c r="D2" t="n">
-        <v>9.468956607460486</v>
+        <v>22.10699480422968</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.71225011166445</v>
+        <v>8.742463306317847</v>
       </c>
       <c r="C3" t="n">
-        <v>19.97856578142259</v>
+        <v>24.12154109334413</v>
       </c>
       <c r="D3" t="n">
-        <v>9.311876974780997</v>
+        <v>5.885577486959629</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39843226314587</v>
+        <v>11.67823469717317</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14473361294012</v>
+        <v>59.94827144548895</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576286148605396</v>
+        <v>0.7785489798115448</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.156719779780995</v>
+        <v>3.367394625566559</v>
       </c>
       <c r="C2" t="n">
-        <v>3.272165098254619</v>
+        <v>5.65388502875738</v>
       </c>
       <c r="D2" t="n">
-        <v>10.15618000043325</v>
+        <v>17.25028891132071</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.70091110756999</v>
+        <v>16.02212253330795</v>
       </c>
       <c r="C3" t="n">
-        <v>18.25559856046944</v>
+        <v>35.49508824704343</v>
       </c>
       <c r="D3" t="n">
-        <v>15.01583113645496</v>
+        <v>23.85646921319749</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.65611056607313</v>
+        <v>10.82278669161684</v>
       </c>
       <c r="C4" t="n">
-        <v>31.47286790274425</v>
+        <v>39.75587328347459</v>
       </c>
       <c r="D4" t="n">
-        <v>19.94813160259094</v>
+        <v>17.21690948937631</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.105088062083415</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44305939473562</v>
+        <v>13.62738691643917</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15601557063033</v>
+        <v>73.74821154778846</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25117039889171</v>
+        <v>1.603221990169314</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.141993564217293</v>
+        <v>2.691952205044754</v>
       </c>
       <c r="C2" t="n">
-        <v>5.821763886183585</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="D2" t="n">
-        <v>9.013425672689966</v>
+        <v>24.23051508851553</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.83559046950105</v>
+        <v>13.55302705712722</v>
       </c>
       <c r="C3" t="n">
-        <v>14.90293015046658</v>
+        <v>26.96860943565988</v>
       </c>
       <c r="D3" t="n">
-        <v>19.65458903902115</v>
+        <v>32.5792975654304</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.25742318715769</v>
+        <v>23.06223532046182</v>
       </c>
       <c r="C4" t="n">
-        <v>39.56443248114646</v>
+        <v>70.19496085364693</v>
       </c>
       <c r="D4" t="n">
-        <v>22.99842171968578</v>
+        <v>25.7168811127452</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.24730261047896</v>
+        <v>10.03837027592364</v>
       </c>
       <c r="C5" t="n">
-        <v>35.95650966803944</v>
+        <v>46.09305471438775</v>
       </c>
       <c r="D5" t="n">
-        <v>29.62423697564751</v>
+        <v>26.08994524035899</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.219371706403542</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74086859470061</v>
+        <v>14.83453209804262</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1192984276737</v>
+        <v>87.35891124402876</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022260578410183</v>
+        <v>2.472422016340437</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.432590884674349</v>
+        <v>2.502474898125119</v>
       </c>
       <c r="C2" t="n">
-        <v>8.418486563916399</v>
+        <v>8.048367679415351</v>
       </c>
       <c r="D2" t="n">
-        <v>24.55841882173396</v>
+        <v>26.67801211520282</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.93729132011522</v>
+        <v>11.16247139728623</v>
       </c>
       <c r="C3" t="n">
-        <v>19.42387832852314</v>
+        <v>21.66226309420587</v>
       </c>
       <c r="D3" t="n">
-        <v>22.13350199224434</v>
+        <v>44.40444866308323</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.10350978176919</v>
+        <v>25.1170332654504</v>
       </c>
       <c r="C4" t="n">
-        <v>38.2881604656256</v>
+        <v>68.68895987533233</v>
       </c>
       <c r="D4" t="n">
-        <v>27.19735665074939</v>
+        <v>36.25888796094745</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.35363446217388</v>
+        <v>22.75200304591983</v>
       </c>
       <c r="C5" t="n">
-        <v>56.3768619163731</v>
+        <v>93.7569057555704</v>
       </c>
       <c r="D5" t="n">
-        <v>31.3668391506856</v>
+        <v>29.30516897176729</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.27046364475338</v>
+        <v>9.298132506921544</v>
       </c>
       <c r="C6" t="n">
-        <v>35.70321876034376</v>
+        <v>44.75984133202059</v>
       </c>
       <c r="D6" t="n">
-        <v>37.79630486579796</v>
+        <v>33.44912603139308</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.70215489718149</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.62343515439249</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.574764375340887</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07520763750187</v>
+        <v>16.07074510530318</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9192117303693</v>
+        <v>100.6536140805831</v>
       </c>
       <c r="D21" t="n">
-        <v>6.885793385714996</v>
+        <v>3.383314759011196</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.461462478725005</v>
+        <v>2.853940576245478</v>
       </c>
       <c r="C2" t="n">
-        <v>11.03288070032565</v>
+        <v>11.99499345048753</v>
       </c>
       <c r="D2" t="n">
-        <v>20.3457394228109</v>
+        <v>33.04170073413065</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.48430471782994</v>
+        <v>9.738937226128359</v>
       </c>
       <c r="C3" t="n">
-        <v>25.56471021858694</v>
+        <v>27.06187546756333</v>
       </c>
       <c r="D3" t="n">
-        <v>33.74266859496287</v>
+        <v>54.80115685105696</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.91809833438679</v>
+        <v>23.35577788403162</v>
       </c>
       <c r="C4" t="n">
-        <v>37.01188845010475</v>
+        <v>60.72502249848221</v>
       </c>
       <c r="D4" t="n">
-        <v>27.58023825540564</v>
+        <v>49.59593052314037</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.73942025221387</v>
+        <v>30.06602344255857</v>
       </c>
       <c r="C5" t="n">
-        <v>47.39387042251478</v>
+        <v>110.3975293425539</v>
       </c>
       <c r="D5" t="n">
-        <v>27.7343726449724</v>
+        <v>35.09748042682348</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.5585166327252</v>
+        <v>19.8843180018149</v>
       </c>
       <c r="C6" t="n">
-        <v>43.71329827929349</v>
+        <v>98.65680854746624</v>
       </c>
       <c r="D6" t="n">
-        <v>30.22899356146354</v>
+        <v>35.50196048097316</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.629341336151211</v>
+        <v>8.743445054022093</v>
       </c>
       <c r="C7" t="n">
-        <v>23.71509754378595</v>
+        <v>41.62119392154352</v>
       </c>
       <c r="D7" t="n">
-        <v>31.38058361854505</v>
+        <v>37.12969817461437</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="C9" t="n">
-        <v>22.18749811597791</v>
+        <v>30.28593492830985</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>38.49530923122167</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>5.858088551240717</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.0678871310458</v>
+        <v>17.32959413030721</v>
       </c>
       <c r="C21" t="n">
-        <v>67.14492774493509</v>
+        <v>114.3753212600276</v>
       </c>
       <c r="D21" t="n">
-        <v>5.30091534828435</v>
+        <v>4.332398532576804</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.178719139901924</v>
+        <v>2.286490403190821</v>
       </c>
       <c r="C2" t="n">
-        <v>8.714974370598936</v>
+        <v>15.43798264928109</v>
       </c>
       <c r="D2" t="n">
-        <v>19.47198396603124</v>
+        <v>36.53377731813656</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.07750131537327</v>
+        <v>9.635853717182444</v>
       </c>
       <c r="C3" t="n">
-        <v>37.27205159173015</v>
+        <v>37.67947688899258</v>
       </c>
       <c r="D3" t="n">
-        <v>43.16744655573225</v>
+        <v>66.13052535806514</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.68310078017331</v>
+        <v>21.00743737547325</v>
       </c>
       <c r="C4" t="n">
-        <v>54.61167954413732</v>
+        <v>63.59663453340413</v>
       </c>
       <c r="D4" t="n">
-        <v>39.43680527959437</v>
+        <v>62.76705772331557</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.19441140763665</v>
+        <v>32.34858685493241</v>
       </c>
       <c r="C5" t="n">
-        <v>60.77018289287758</v>
+        <v>111.1583838133451</v>
       </c>
       <c r="D5" t="n">
-        <v>31.71045084717198</v>
+        <v>43.85957868722626</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.93715245139498</v>
+        <v>29.58496706747763</v>
       </c>
       <c r="C6" t="n">
-        <v>63.07434475474484</v>
+        <v>135.6078286399077</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>38.03781480104267</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.19879606234337</v>
+        <v>15.4507453694363</v>
       </c>
       <c r="C7" t="n">
-        <v>47.54996830749001</v>
+        <v>88.57229612944299</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>39.16584291322225</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>8.678649705541805</v>
       </c>
       <c r="C8" t="n">
-        <v>26.62008900065226</v>
+        <v>39.55461500410399</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>39.49374664644068</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>46.02335062738621</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>32.26022956155019</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.295948745844007</v>
+        <v>17.717198654542</v>
       </c>
       <c r="C21" t="n">
-        <v>77.51945542459258</v>
+        <v>127.5638303127024</v>
       </c>
       <c r="D21" t="n">
-        <v>6.383955152613506</v>
+        <v>5.315159596362601</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.228387362191013</v>
+        <v>2.156899706230242</v>
       </c>
       <c r="C2" t="n">
-        <v>6.601271563355553</v>
+        <v>9.756608684804801</v>
       </c>
       <c r="D2" t="n">
-        <v>24.20989838672634</v>
+        <v>28.89578017909637</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.63218876827272</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C3" t="n">
-        <v>35.22510762837555</v>
+        <v>57.82493978013713</v>
       </c>
       <c r="D3" t="n">
-        <v>48.72904730029043</v>
+        <v>72.08973392284329</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.63503620039422</v>
+        <v>15.53223042888879</v>
       </c>
       <c r="C4" t="n">
-        <v>77.30379598009809</v>
+        <v>93.94638306249003</v>
       </c>
       <c r="D4" t="n">
-        <v>51.82940655030185</v>
+        <v>57.49605429921445</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.13398501832986</v>
+        <v>16.66516727958961</v>
       </c>
       <c r="C5" t="n">
-        <v>84.55302102825655</v>
+        <v>81.01872929296803</v>
       </c>
       <c r="D5" t="n">
-        <v>39.19627709205391</v>
+        <v>35.34291735288518</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.30949687321178</v>
+        <v>9.579894098040377</v>
       </c>
       <c r="C6" t="n">
-        <v>82.31463626257383</v>
+        <v>58.32464936159877</v>
       </c>
       <c r="D6" t="n">
-        <v>35.54221213684728</v>
+        <v>25.76105975943631</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.64280806657018</v>
+        <v>5.749114556069321</v>
       </c>
       <c r="C7" t="n">
-        <v>72.46279805045707</v>
+        <v>27.78738702100172</v>
       </c>
       <c r="D7" t="n">
-        <v>36.17151241526948</v>
+        <v>26.70942804173872</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.346238144429634</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>47.14843349645307</v>
+        <v>23.19869825135213</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>29.06562253193106</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.83959354690535</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.512033913525388</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>87.32739424473263</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.512033913525388</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
